--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_packaging_container.xlsx
@@ -1127,43 +1127,43 @@
         <v>0.773584905660377</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>142.042481950403</v>
       </c>
       <c r="G2">
         <v>7.41269841269841</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.120634920634921</v>
       </c>
       <c r="I2">
         <v>0.614473684210526</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>87.90000000000001</v>
       </c>
       <c r="L2">
-        <v>268.042087736281</v>
+        <v>265.459924602881</v>
       </c>
       <c r="M2">
         <v>172.8</v>
       </c>
       <c r="N2">
-        <v>212.842087736281</v>
+        <v>212.53992460288</v>
       </c>
       <c r="O2">
         <v>140.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q2">
         <v>0.0847874950463019</v>
       </c>
       <c r="R2">
-        <v>0.07745275822866581</v>
+        <v>0.07749775822866579</v>
       </c>
       <c r="S2">
         <v>0.0577366166625341</v>
@@ -1185,13 +1185,13 @@
         <v>0.127902717589713</v>
       </c>
       <c r="X2">
-        <v>0.07745275822866581</v>
+        <v>0.07777248305925839</v>
       </c>
       <c r="Y2">
         <v>1.6003347835314</v>
       </c>
       <c r="Z2">
-        <v>0.616971173124606</v>
+        <v>0.62320320517637</v>
       </c>
       <c r="AA2">
         <v>140.1</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07745275822866582</v>
+        <v>0.07749775822866582</v>
       </c>
       <c r="C2">
-        <v>268.0420877362806</v>
+        <v>265.4599246028805</v>
       </c>
       <c r="D2">
-        <v>212.8420877362806</v>
+        <v>212.5399246028805</v>
       </c>
       <c r="E2">
-        <v>-140.1</v>
+        <v>-137.82</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
         <v>55.2</v>
@@ -1445,28 +1445,28 @@
         <v>16.29</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.114684</v>
       </c>
       <c r="N2">
-        <v>16.29</v>
+        <v>16.175316</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>16.29</v>
+        <v>16.175316</v>
       </c>
       <c r="Q2">
-        <v>31.5</v>
+        <v>31.385316</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07745275822866582</v>
+        <v>0.07777248305925841</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6232032051763696</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>142.0424819504028</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07749775822866582</v>
+        <v>0.0775427582286658</v>
       </c>
       <c r="C3">
-        <v>265.4599246028805</v>
+        <v>262.8786181903052</v>
       </c>
       <c r="D3">
-        <v>212.5399246028805</v>
+        <v>212.2386181903052</v>
       </c>
       <c r="E3">
-        <v>-137.82</v>
+        <v>-135.54</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>4.56</v>
       </c>
       <c r="G3">
         <v>55.2</v>
@@ -1527,28 +1527,28 @@
         <v>16.29</v>
       </c>
       <c r="M3">
-        <v>0.114684</v>
+        <v>0.229368</v>
       </c>
       <c r="N3">
-        <v>16.175316</v>
+        <v>16.060632</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>16.175316</v>
+        <v>16.060632</v>
       </c>
       <c r="Q3">
-        <v>31.385316</v>
+        <v>31.270632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07777248305925841</v>
+        <v>0.07809873288639368</v>
       </c>
       <c r="T3">
-        <v>0.6232032051763696</v>
+        <v>0.6295624215557203</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.0424819504028</v>
+        <v>71.02124097520141</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0775427582286658</v>
+        <v>0.0775877582286658</v>
       </c>
       <c r="C4">
-        <v>262.8786181903052</v>
+        <v>260.2981648601314</v>
       </c>
       <c r="D4">
-        <v>212.2386181903052</v>
+        <v>211.9381648601313</v>
       </c>
       <c r="E4">
-        <v>-135.54</v>
+        <v>-133.26</v>
       </c>
       <c r="F4">
-        <v>4.56</v>
+        <v>6.84</v>
       </c>
       <c r="G4">
         <v>55.2</v>
@@ -1609,28 +1609,28 @@
         <v>16.29</v>
       </c>
       <c r="M4">
-        <v>0.229368</v>
+        <v>0.344052</v>
       </c>
       <c r="N4">
-        <v>16.060632</v>
+        <v>15.945948</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>16.060632</v>
+        <v>15.945948</v>
       </c>
       <c r="Q4">
-        <v>31.270632</v>
+        <v>31.155948</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07809873288639368</v>
+        <v>0.07843170951408845</v>
       </c>
       <c r="T4">
-        <v>0.6295624215557203</v>
+        <v>0.6360527557985627</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.02124097520141</v>
+        <v>47.34749398346761</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0775877582286658</v>
+        <v>0.0776327582286658</v>
       </c>
       <c r="C5">
-        <v>260.2981648601314</v>
+        <v>257.7185609945097</v>
       </c>
       <c r="D5">
-        <v>211.9381648601313</v>
+        <v>211.6385609945097</v>
       </c>
       <c r="E5">
-        <v>-133.26</v>
+        <v>-130.98</v>
       </c>
       <c r="F5">
-        <v>6.84</v>
+        <v>9.120000000000001</v>
       </c>
       <c r="G5">
         <v>55.2</v>
@@ -1691,28 +1691,28 @@
         <v>16.29</v>
       </c>
       <c r="M5">
-        <v>0.344052</v>
+        <v>0.458736</v>
       </c>
       <c r="N5">
-        <v>15.945948</v>
+        <v>15.831264</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>15.945948</v>
+        <v>15.831264</v>
       </c>
       <c r="Q5">
-        <v>31.155948</v>
+        <v>31.041264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07843170951408845</v>
+        <v>0.07877162315486022</v>
       </c>
       <c r="T5">
-        <v>0.6360527557985627</v>
+        <v>0.6426783053381312</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.34749398346761</v>
+        <v>35.5106204876007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0776327582286658</v>
+        <v>0.07767775822866581</v>
       </c>
       <c r="C6">
-        <v>257.7185609945097</v>
+        <v>255.1398029960194</v>
       </c>
       <c r="D6">
-        <v>211.6385609945097</v>
+        <v>211.3398029960194</v>
       </c>
       <c r="E6">
-        <v>-130.98</v>
+        <v>-128.7</v>
       </c>
       <c r="F6">
-        <v>9.120000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="G6">
         <v>55.2</v>
@@ -1773,28 +1773,28 @@
         <v>16.29</v>
       </c>
       <c r="M6">
-        <v>0.458736</v>
+        <v>0.57342</v>
       </c>
       <c r="N6">
-        <v>15.831264</v>
+        <v>15.71658</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>15.831264</v>
+        <v>15.71658</v>
       </c>
       <c r="Q6">
-        <v>31.041264</v>
+        <v>30.92658</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07877162315486022</v>
+        <v>0.07911869287227979</v>
       </c>
       <c r="T6">
-        <v>0.6426783053381312</v>
+        <v>0.6494433401311641</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.5106204876007</v>
+        <v>28.40849639008056</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07767775822866581</v>
+        <v>0.07772275822866581</v>
       </c>
       <c r="C7">
-        <v>255.1398029960194</v>
+        <v>252.561887287524</v>
       </c>
       <c r="D7">
-        <v>211.3398029960194</v>
+        <v>211.041887287524</v>
       </c>
       <c r="E7">
-        <v>-128.7</v>
+        <v>-126.42</v>
       </c>
       <c r="F7">
-        <v>11.4</v>
+        <v>13.68</v>
       </c>
       <c r="G7">
         <v>55.2</v>
@@ -1855,28 +1855,28 @@
         <v>16.29</v>
       </c>
       <c r="M7">
-        <v>0.57342</v>
+        <v>0.688104</v>
       </c>
       <c r="N7">
-        <v>15.71658</v>
+        <v>15.601896</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>15.71658</v>
+        <v>15.601896</v>
       </c>
       <c r="Q7">
-        <v>30.92658</v>
+        <v>30.811896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07911869287227979</v>
+        <v>0.07947314705177214</v>
       </c>
       <c r="T7">
-        <v>0.6494433401311641</v>
+        <v>0.6563523118346871</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.40849639008056</v>
+        <v>23.67374699173381</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07772275822866581</v>
+        <v>0.07776775822866581</v>
       </c>
       <c r="C8">
-        <v>252.561887287524</v>
+        <v>249.9848103120286</v>
       </c>
       <c r="D8">
-        <v>211.041887287524</v>
+        <v>210.7448103120286</v>
       </c>
       <c r="E8">
-        <v>-126.42</v>
+        <v>-124.14</v>
       </c>
       <c r="F8">
-        <v>13.68</v>
+        <v>15.96</v>
       </c>
       <c r="G8">
         <v>55.2</v>
@@ -1937,28 +1937,28 @@
         <v>16.29</v>
       </c>
       <c r="M8">
-        <v>0.6881039999999999</v>
+        <v>0.8027879999999999</v>
       </c>
       <c r="N8">
-        <v>15.601896</v>
+        <v>15.487212</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>15.601896</v>
+        <v>15.487212</v>
       </c>
       <c r="Q8">
-        <v>30.811896</v>
+        <v>30.697212</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07947314705177214</v>
+        <v>0.07983522390179119</v>
       </c>
       <c r="T8">
-        <v>0.6563523118346871</v>
+        <v>0.663409863574845</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.67374699173381</v>
+        <v>20.29178313577184</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0777677582286658</v>
+        <v>0.07781275822866582</v>
       </c>
       <c r="C9">
-        <v>249.9848103120287</v>
+        <v>247.4085685325387</v>
       </c>
       <c r="D9">
-        <v>210.7448103120287</v>
+        <v>210.4485685325386</v>
       </c>
       <c r="E9">
-        <v>-124.14</v>
+        <v>-121.86</v>
       </c>
       <c r="F9">
-        <v>15.96</v>
+        <v>18.24</v>
       </c>
       <c r="G9">
         <v>55.2</v>
@@ -2019,28 +2019,28 @@
         <v>16.29</v>
       </c>
       <c r="M9">
-        <v>0.8027880000000001</v>
+        <v>0.9174720000000001</v>
       </c>
       <c r="N9">
-        <v>15.487212</v>
+        <v>15.372528</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>15.487212</v>
+        <v>15.372528</v>
       </c>
       <c r="Q9">
-        <v>30.697212</v>
+        <v>30.582528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07983522390179119</v>
+        <v>0.08020517198768023</v>
       </c>
       <c r="T9">
-        <v>0.663409863574845</v>
+        <v>0.6706208403528325</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.29178313577183</v>
+        <v>17.75531024380035</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07781275822866582</v>
+        <v>0.07785775822866582</v>
       </c>
       <c r="C10">
-        <v>247.4085685325387</v>
+        <v>244.8331584319191</v>
       </c>
       <c r="D10">
-        <v>210.4485685325386</v>
+        <v>210.1531584319192</v>
       </c>
       <c r="E10">
-        <v>-121.86</v>
+        <v>-119.58</v>
       </c>
       <c r="F10">
-        <v>18.24</v>
+        <v>20.52</v>
       </c>
       <c r="G10">
         <v>55.2</v>
@@ -2101,28 +2101,28 @@
         <v>16.29</v>
       </c>
       <c r="M10">
-        <v>0.9174720000000001</v>
+        <v>1.032156</v>
       </c>
       <c r="N10">
-        <v>15.372528</v>
+        <v>15.257844</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>15.372528</v>
+        <v>15.257844</v>
       </c>
       <c r="Q10">
-        <v>30.582528</v>
+        <v>30.467844</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08020517198768023</v>
+        <v>0.08058325080073167</v>
       </c>
       <c r="T10">
-        <v>0.6706208403528325</v>
+        <v>0.6779903001369296</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.75531024380035</v>
+        <v>15.78249799448921</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07785775822866582</v>
+        <v>0.07790275822866582</v>
       </c>
       <c r="C11">
-        <v>244.8331584319191</v>
+        <v>242.2585765127558</v>
       </c>
       <c r="D11">
-        <v>210.1531584319192</v>
+        <v>209.8585765127558</v>
       </c>
       <c r="E11">
-        <v>-119.58</v>
+        <v>-117.3</v>
       </c>
       <c r="F11">
-        <v>20.52</v>
+        <v>22.8</v>
       </c>
       <c r="G11">
         <v>55.2</v>
@@ -2183,28 +2183,28 @@
         <v>16.29</v>
       </c>
       <c r="M11">
-        <v>1.032156</v>
+        <v>1.14684</v>
       </c>
       <c r="N11">
-        <v>15.257844</v>
+        <v>15.14316</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>15.257844</v>
+        <v>15.14316</v>
       </c>
       <c r="Q11">
-        <v>30.467844</v>
+        <v>30.35316</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08058325080073167</v>
+        <v>0.08096973136518423</v>
       </c>
       <c r="T11">
-        <v>0.6779903001369296</v>
+        <v>0.6855235256940067</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.78249799448921</v>
+        <v>14.20424819504029</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07790275822866582</v>
+        <v>0.07794775822866581</v>
       </c>
       <c r="C12">
-        <v>242.2585765127558</v>
+        <v>239.6848192972169</v>
       </c>
       <c r="D12">
-        <v>209.8585765127558</v>
+        <v>209.5648192972169</v>
       </c>
       <c r="E12">
-        <v>-117.3</v>
+        <v>-115.02</v>
       </c>
       <c r="F12">
-        <v>22.8</v>
+        <v>25.08</v>
       </c>
       <c r="G12">
         <v>55.2</v>
@@ -2265,28 +2265,28 @@
         <v>16.29</v>
       </c>
       <c r="M12">
-        <v>1.14684</v>
+        <v>1.261524</v>
       </c>
       <c r="N12">
-        <v>15.14316</v>
+        <v>15.028476</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>15.14316</v>
+        <v>15.028476</v>
       </c>
       <c r="Q12">
-        <v>30.35316</v>
+        <v>30.238476</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08096973136518423</v>
+        <v>0.08136489688614137</v>
       </c>
       <c r="T12">
-        <v>0.6855235256940067</v>
+        <v>0.6932260372186584</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.20424819504028</v>
+        <v>12.91295290458208</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07794775822866581</v>
+        <v>0.0781727582286658</v>
       </c>
       <c r="C13">
-        <v>239.6848192972169</v>
+        <v>235.9482834034011</v>
       </c>
       <c r="D13">
-        <v>209.5648192972169</v>
+        <v>208.1082834034011</v>
       </c>
       <c r="E13">
-        <v>-115.02</v>
+        <v>-112.74</v>
       </c>
       <c r="F13">
-        <v>25.08</v>
+        <v>27.36</v>
       </c>
       <c r="G13">
         <v>55.2</v>
@@ -2347,45 +2347,45 @@
         <v>16.29</v>
       </c>
       <c r="M13">
-        <v>1.261524</v>
+        <v>1.417248</v>
       </c>
       <c r="N13">
-        <v>15.028476</v>
+        <v>14.872752</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>15.028476</v>
+        <v>14.872752</v>
       </c>
       <c r="Q13">
-        <v>30.238476</v>
+        <v>30.082752</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08136489688614137</v>
+        <v>0.08176904344166569</v>
       </c>
       <c r="T13">
-        <v>0.6932260372186584</v>
+        <v>0.7011036058234158</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.91295290458208</v>
+        <v>11.49410688884373</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0781727582286658</v>
+        <v>0.07823275822866582</v>
       </c>
       <c r="C14">
-        <v>235.9482834034011</v>
+        <v>233.2832869465419</v>
       </c>
       <c r="D14">
-        <v>208.1082834034011</v>
+        <v>207.7232869465419</v>
       </c>
       <c r="E14">
-        <v>-112.74</v>
+        <v>-110.46</v>
       </c>
       <c r="F14">
-        <v>27.36</v>
+        <v>29.64</v>
       </c>
       <c r="G14">
         <v>55.2</v>
@@ -2429,28 +2429,28 @@
         <v>16.29</v>
       </c>
       <c r="M14">
-        <v>1.417248</v>
+        <v>1.535352</v>
       </c>
       <c r="N14">
-        <v>14.872752</v>
+        <v>14.754648</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>14.872752</v>
+        <v>14.754648</v>
       </c>
       <c r="Q14">
-        <v>30.082752</v>
+        <v>29.964648</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08176904344166569</v>
+        <v>0.08218248072260438</v>
       </c>
       <c r="T14">
-        <v>0.7011036058234158</v>
+        <v>0.7091622679593171</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.49410688884373</v>
+        <v>10.60994482047114</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07823275822866582</v>
+        <v>0.07829275822866581</v>
       </c>
       <c r="C15">
-        <v>233.2832869465419</v>
+        <v>230.6197123318822</v>
       </c>
       <c r="D15">
-        <v>207.7232869465419</v>
+        <v>207.3397123318822</v>
       </c>
       <c r="E15">
-        <v>-110.46</v>
+        <v>-108.18</v>
       </c>
       <c r="F15">
-        <v>29.64</v>
+        <v>31.92</v>
       </c>
       <c r="G15">
         <v>55.2</v>
@@ -2511,28 +2511,28 @@
         <v>16.29</v>
       </c>
       <c r="M15">
-        <v>1.535352</v>
+        <v>1.653456</v>
       </c>
       <c r="N15">
-        <v>14.754648</v>
+        <v>14.636544</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>14.754648</v>
+        <v>14.636544</v>
       </c>
       <c r="Q15">
-        <v>29.964648</v>
+        <v>29.846544</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08218248072260438</v>
+        <v>0.08260553282403002</v>
       </c>
       <c r="T15">
-        <v>0.7091622679593171</v>
+        <v>0.7174083408425651</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.60994482047114</v>
+        <v>9.852091619008911</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07829275822866581</v>
+        <v>0.07860775822866582</v>
       </c>
       <c r="C16">
-        <v>230.6197123318822</v>
+        <v>226.3489634081268</v>
       </c>
       <c r="D16">
-        <v>207.3397123318822</v>
+        <v>205.3489634081268</v>
       </c>
       <c r="E16">
-        <v>-108.18</v>
+        <v>-105.9</v>
       </c>
       <c r="F16">
-        <v>31.92</v>
+        <v>34.2</v>
       </c>
       <c r="G16">
         <v>55.2</v>
@@ -2593,45 +2593,45 @@
         <v>16.29</v>
       </c>
       <c r="M16">
-        <v>1.653456</v>
+        <v>1.8297</v>
       </c>
       <c r="N16">
-        <v>14.636544</v>
+        <v>14.4603</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>14.636544</v>
+        <v>14.4603</v>
       </c>
       <c r="Q16">
-        <v>29.846544</v>
+        <v>29.6703</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08260553282403002</v>
+        <v>0.08303853909254802</v>
       </c>
       <c r="T16">
-        <v>0.7174083408425651</v>
+        <v>0.7258484389701246</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.852091619008911</v>
+        <v>8.903098868666994</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07860775822866582</v>
+        <v>0.07868475822866582</v>
       </c>
       <c r="C17">
-        <v>226.3489634081268</v>
+        <v>223.5881366958707</v>
       </c>
       <c r="D17">
-        <v>205.3489634081268</v>
+        <v>204.8681366958708</v>
       </c>
       <c r="E17">
-        <v>-105.9</v>
+        <v>-103.62</v>
       </c>
       <c r="F17">
-        <v>34.2</v>
+        <v>36.48</v>
       </c>
       <c r="G17">
         <v>55.2</v>
@@ -2675,28 +2675,28 @@
         <v>16.29</v>
       </c>
       <c r="M17">
-        <v>1.8297</v>
+        <v>1.95168</v>
       </c>
       <c r="N17">
-        <v>14.4603</v>
+        <v>14.33832</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>14.4603</v>
+        <v>14.33832</v>
       </c>
       <c r="Q17">
-        <v>29.6703</v>
+        <v>29.54832</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08303853909254802</v>
+        <v>0.08348185503412597</v>
       </c>
       <c r="T17">
-        <v>0.7258484389701246</v>
+        <v>0.734489491815007</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.903098868666996</v>
+        <v>8.346655189375307</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07868475822866582</v>
+        <v>0.07876175822866582</v>
       </c>
       <c r="C18">
-        <v>223.5881366958707</v>
+        <v>220.8295564448978</v>
       </c>
       <c r="D18">
-        <v>204.8681366958708</v>
+        <v>204.3895564448978</v>
       </c>
       <c r="E18">
-        <v>-103.62</v>
+        <v>-101.34</v>
       </c>
       <c r="F18">
-        <v>36.48</v>
+        <v>38.76000000000001</v>
       </c>
       <c r="G18">
         <v>55.2</v>
@@ -2757,28 +2757,28 @@
         <v>16.29</v>
       </c>
       <c r="M18">
-        <v>1.95168</v>
+        <v>2.07366</v>
       </c>
       <c r="N18">
-        <v>14.33832</v>
+        <v>14.21634</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>14.33832</v>
+        <v>14.21634</v>
       </c>
       <c r="Q18">
-        <v>29.54832</v>
+        <v>29.42634</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08348185503412597</v>
+        <v>0.08393585328754918</v>
       </c>
       <c r="T18">
-        <v>0.734489491815007</v>
+        <v>0.7433387628007301</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.346655189375307</v>
+        <v>7.855675472353229</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07876175822866582</v>
+        <v>0.07898275822866581</v>
       </c>
       <c r="C19">
-        <v>220.8295564448978</v>
+        <v>217.1883045663455</v>
       </c>
       <c r="D19">
-        <v>204.3895564448978</v>
+        <v>203.0283045663455</v>
       </c>
       <c r="E19">
-        <v>-101.34</v>
+        <v>-99.05999999999999</v>
       </c>
       <c r="F19">
-        <v>38.76000000000001</v>
+        <v>41.04000000000001</v>
       </c>
       <c r="G19">
         <v>55.2</v>
@@ -2839,45 +2839,45 @@
         <v>16.29</v>
       </c>
       <c r="M19">
-        <v>2.07366</v>
+        <v>2.228472</v>
       </c>
       <c r="N19">
-        <v>14.21634</v>
+        <v>14.061528</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>14.21634</v>
+        <v>14.061528</v>
       </c>
       <c r="Q19">
-        <v>29.42634</v>
+        <v>29.271528</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08393585328754918</v>
+        <v>0.08440092466910465</v>
       </c>
       <c r="T19">
-        <v>0.7433387628007301</v>
+        <v>0.7524038696641535</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.855675472353229</v>
+        <v>7.309941520467834</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07898275822866582</v>
+        <v>0.07906775822866582</v>
       </c>
       <c r="C20">
-        <v>217.1883045663454</v>
+        <v>214.3895618915453</v>
       </c>
       <c r="D20">
-        <v>203.0283045663454</v>
+        <v>202.5095618915453</v>
       </c>
       <c r="E20">
-        <v>-99.06</v>
+        <v>-96.78</v>
       </c>
       <c r="F20">
-        <v>41.04</v>
+        <v>43.32</v>
       </c>
       <c r="G20">
         <v>55.2</v>
@@ -2921,28 +2921,28 @@
         <v>16.29</v>
       </c>
       <c r="M20">
-        <v>2.228472</v>
+        <v>2.352276</v>
       </c>
       <c r="N20">
-        <v>14.061528</v>
+        <v>13.937724</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>14.061528</v>
+        <v>13.937724</v>
       </c>
       <c r="Q20">
-        <v>29.271528</v>
+        <v>29.147724</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08440092466910465</v>
+        <v>0.08487747929464914</v>
       </c>
       <c r="T20">
-        <v>0.7524038696641535</v>
+        <v>0.7616928063266739</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.309941520467836</v>
+        <v>6.925207756232686</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07906775822866582</v>
+        <v>0.0791527582286658</v>
       </c>
       <c r="C21">
-        <v>214.3895618915453</v>
+        <v>211.5934632635769</v>
       </c>
       <c r="D21">
-        <v>202.5095618915453</v>
+        <v>201.9934632635769</v>
       </c>
       <c r="E21">
-        <v>-96.78</v>
+        <v>-94.5</v>
       </c>
       <c r="F21">
-        <v>43.32</v>
+        <v>45.6</v>
       </c>
       <c r="G21">
         <v>55.2</v>
@@ -3003,28 +3003,28 @@
         <v>16.29</v>
       </c>
       <c r="M21">
-        <v>2.352276</v>
+        <v>2.47608</v>
       </c>
       <c r="N21">
-        <v>13.937724</v>
+        <v>13.81392</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>13.937724</v>
+        <v>13.81392</v>
       </c>
       <c r="Q21">
-        <v>29.147724</v>
+        <v>29.02392</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08487747929464914</v>
+        <v>0.08536594778583226</v>
       </c>
       <c r="T21">
-        <v>0.7616928063266739</v>
+        <v>0.7712139664057573</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.925207756232686</v>
+        <v>6.578947368421052</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0791527582286658</v>
+        <v>0.07923775822866581</v>
       </c>
       <c r="C22">
-        <v>211.5934632635769</v>
+        <v>208.7999885186496</v>
       </c>
       <c r="D22">
-        <v>201.9934632635769</v>
+        <v>201.4799885186496</v>
       </c>
       <c r="E22">
-        <v>-94.5</v>
+        <v>-92.22</v>
       </c>
       <c r="F22">
-        <v>45.6</v>
+        <v>47.88</v>
       </c>
       <c r="G22">
         <v>55.2</v>
@@ -3085,28 +3085,28 @@
         <v>16.29</v>
       </c>
       <c r="M22">
-        <v>2.47608</v>
+        <v>2.599884</v>
       </c>
       <c r="N22">
-        <v>13.81392</v>
+        <v>13.690116</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>13.81392</v>
+        <v>13.690116</v>
       </c>
       <c r="Q22">
-        <v>29.02392</v>
+        <v>28.900116</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08536594778583226</v>
+        <v>0.08586678256793141</v>
       </c>
       <c r="T22">
-        <v>0.7712139664057573</v>
+        <v>0.7809761685121595</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.578947368421052</v>
+        <v>6.265664160401002</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07923775822866581</v>
+        <v>0.07954275822866581</v>
       </c>
       <c r="C23">
-        <v>208.7999885186496</v>
+        <v>204.6988156292922</v>
       </c>
       <c r="D23">
-        <v>201.4799885186496</v>
+        <v>199.6588156292921</v>
       </c>
       <c r="E23">
-        <v>-92.22</v>
+        <v>-89.94</v>
       </c>
       <c r="F23">
-        <v>47.88</v>
+        <v>50.16</v>
       </c>
       <c r="G23">
         <v>55.2</v>
@@ -3167,45 +3167,45 @@
         <v>16.29</v>
       </c>
       <c r="M23">
-        <v>2.599884</v>
+        <v>2.773848</v>
       </c>
       <c r="N23">
-        <v>13.690116</v>
+        <v>13.516152</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>13.690116</v>
+        <v>13.516152</v>
       </c>
       <c r="Q23">
-        <v>28.900116</v>
+        <v>28.726152</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08586678256793141</v>
+        <v>0.08638045926752028</v>
       </c>
       <c r="T23">
-        <v>0.7809761685121595</v>
+        <v>0.7909886834930845</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.265664160401003</v>
+        <v>5.872708237798177</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07954275822866581</v>
+        <v>0.07963775822866581</v>
       </c>
       <c r="C24">
-        <v>204.6988156292922</v>
+        <v>201.858270590918</v>
       </c>
       <c r="D24">
-        <v>199.6588156292921</v>
+        <v>199.098270590918</v>
       </c>
       <c r="E24">
-        <v>-89.94</v>
+        <v>-87.66</v>
       </c>
       <c r="F24">
-        <v>50.16</v>
+        <v>52.44</v>
       </c>
       <c r="G24">
         <v>55.2</v>
@@ -3249,28 +3249,28 @@
         <v>16.29</v>
       </c>
       <c r="M24">
-        <v>2.773848</v>
+        <v>2.899932</v>
       </c>
       <c r="N24">
-        <v>13.516152</v>
+        <v>13.390068</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>13.516152</v>
+        <v>13.390068</v>
       </c>
       <c r="Q24">
-        <v>28.726152</v>
+        <v>28.600068</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08638045926752028</v>
+        <v>0.08690747821904651</v>
       </c>
       <c r="T24">
-        <v>0.7909886834930845</v>
+        <v>0.8012612637981895</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.872708237798177</v>
+        <v>5.617373097024344</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07963775822866581</v>
+        <v>0.07973275822866582</v>
       </c>
       <c r="C25">
-        <v>201.858270590918</v>
+        <v>199.0208642174461</v>
       </c>
       <c r="D25">
-        <v>199.098270590918</v>
+        <v>198.5408642174461</v>
       </c>
       <c r="E25">
-        <v>-87.66</v>
+        <v>-85.38</v>
       </c>
       <c r="F25">
-        <v>52.44</v>
+        <v>54.72000000000001</v>
       </c>
       <c r="G25">
         <v>55.2</v>
@@ -3331,28 +3331,28 @@
         <v>16.29</v>
       </c>
       <c r="M25">
-        <v>2.899932</v>
+        <v>3.026016</v>
       </c>
       <c r="N25">
-        <v>13.390068</v>
+        <v>13.263984</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>13.390068</v>
+        <v>13.263984</v>
       </c>
       <c r="Q25">
-        <v>28.600068</v>
+        <v>28.473984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08690747821904651</v>
+        <v>0.08744836609034976</v>
       </c>
       <c r="T25">
-        <v>0.8012612637981895</v>
+        <v>0.8118041751639552</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.617373097024344</v>
+        <v>5.383315884648329</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07973275822866582</v>
+        <v>0.07982775822866582</v>
       </c>
       <c r="C26">
-        <v>199.0208642174461</v>
+        <v>196.1865702209416</v>
       </c>
       <c r="D26">
-        <v>198.5408642174461</v>
+        <v>197.9865702209416</v>
       </c>
       <c r="E26">
-        <v>-85.38</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="F26">
-        <v>54.72</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>55.2</v>
@@ -3413,28 +3413,28 @@
         <v>16.29</v>
       </c>
       <c r="M26">
-        <v>3.026016</v>
+        <v>3.1521</v>
       </c>
       <c r="N26">
-        <v>13.263984</v>
+        <v>13.1379</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>13.263984</v>
+        <v>13.1379</v>
       </c>
       <c r="Q26">
-        <v>28.473984</v>
+        <v>28.3479</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08744836609034976</v>
+        <v>0.08800367763822109</v>
       </c>
       <c r="T26">
-        <v>0.8118041751639552</v>
+        <v>0.8226282308328079</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.383315884648329</v>
+        <v>5.167983249262396</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07982775822866582</v>
+        <v>0.07992275822866581</v>
       </c>
       <c r="C27">
-        <v>196.1865702209416</v>
+        <v>193.3553626062187</v>
       </c>
       <c r="D27">
-        <v>197.9865702209416</v>
+        <v>197.4353626062187</v>
       </c>
       <c r="E27">
-        <v>-83.09999999999999</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="F27">
-        <v>57</v>
+        <v>59.28</v>
       </c>
       <c r="G27">
         <v>55.2</v>
@@ -3495,28 +3495,28 @@
         <v>16.29</v>
       </c>
       <c r="M27">
-        <v>3.1521</v>
+        <v>3.278184</v>
       </c>
       <c r="N27">
-        <v>13.1379</v>
+        <v>13.011816</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>13.1379</v>
+        <v>13.011816</v>
       </c>
       <c r="Q27">
-        <v>28.3479</v>
+        <v>28.221816</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08800367763822109</v>
+        <v>0.08857399760630515</v>
       </c>
       <c r="T27">
-        <v>0.8226282308328079</v>
+        <v>0.8337448285467647</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.167983249262396</v>
+        <v>4.969214662752304</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07992275822866581</v>
+        <v>0.08001775822866582</v>
       </c>
       <c r="C28">
-        <v>193.3553626062187</v>
+        <v>190.5272156667772</v>
       </c>
       <c r="D28">
-        <v>197.4353626062187</v>
+        <v>196.8872156667773</v>
       </c>
       <c r="E28">
-        <v>-80.81999999999999</v>
+        <v>-78.53999999999999</v>
       </c>
       <c r="F28">
-        <v>59.28</v>
+        <v>61.56</v>
       </c>
       <c r="G28">
         <v>55.2</v>
@@ -3577,28 +3577,28 @@
         <v>16.29</v>
       </c>
       <c r="M28">
-        <v>3.278184</v>
+        <v>3.404268</v>
       </c>
       <c r="N28">
-        <v>13.011816</v>
+        <v>12.885732</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>13.011816</v>
+        <v>12.885732</v>
       </c>
       <c r="Q28">
-        <v>28.221816</v>
+        <v>28.095732</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08857399760630515</v>
+        <v>0.08915994277899426</v>
       </c>
       <c r="T28">
-        <v>0.8337448285467647</v>
+        <v>0.845165990581652</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.969214662752304</v>
+        <v>4.78516967524296</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08001775822866582</v>
+        <v>0.0801127582286658</v>
       </c>
       <c r="C29">
-        <v>190.5272156667772</v>
+        <v>187.7021039808063</v>
       </c>
       <c r="D29">
-        <v>196.8872156667773</v>
+        <v>196.3421039808063</v>
       </c>
       <c r="E29">
-        <v>-78.53999999999999</v>
+        <v>-76.25999999999999</v>
       </c>
       <c r="F29">
-        <v>61.56</v>
+        <v>63.84</v>
       </c>
       <c r="G29">
         <v>55.2</v>
@@ -3659,28 +3659,28 @@
         <v>16.29</v>
       </c>
       <c r="M29">
-        <v>3.404268</v>
+        <v>3.530352</v>
       </c>
       <c r="N29">
-        <v>12.885732</v>
+        <v>12.759648</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>12.885732</v>
+        <v>12.759648</v>
       </c>
       <c r="Q29">
-        <v>28.095732</v>
+        <v>27.969648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08915994277899426</v>
+        <v>0.08976216420648028</v>
       </c>
       <c r="T29">
-        <v>0.845165990581652</v>
+        <v>0.8569044071175081</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.78516967524296</v>
+        <v>4.614270758269996</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0801127582286658</v>
+        <v>0.0809327582286658</v>
       </c>
       <c r="C30">
-        <v>187.7021039808063</v>
+        <v>180.839471321669</v>
       </c>
       <c r="D30">
-        <v>196.3421039808063</v>
+        <v>191.7594713216689</v>
       </c>
       <c r="E30">
-        <v>-76.25999999999999</v>
+        <v>-73.97999999999999</v>
       </c>
       <c r="F30">
-        <v>63.84</v>
+        <v>66.12</v>
       </c>
       <c r="G30">
         <v>55.2</v>
@@ -3741,45 +3741,45 @@
         <v>16.29</v>
       </c>
       <c r="M30">
-        <v>3.530352</v>
+        <v>3.821736</v>
       </c>
       <c r="N30">
-        <v>12.759648</v>
+        <v>12.468264</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>12.759648</v>
+        <v>12.468264</v>
       </c>
       <c r="Q30">
-        <v>27.969648</v>
+        <v>27.678264</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08976216420648028</v>
+        <v>0.09038134961783917</v>
       </c>
       <c r="T30">
-        <v>0.8569044071175081</v>
+        <v>0.868973483274093</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.614270758269996</v>
+        <v>4.262460829319449</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0809327582286658</v>
+        <v>0.08105275822866581</v>
       </c>
       <c r="C31">
-        <v>180.839471321669</v>
+        <v>177.906724197335</v>
       </c>
       <c r="D31">
-        <v>191.7594713216689</v>
+        <v>191.106724197335</v>
       </c>
       <c r="E31">
-        <v>-73.98</v>
+        <v>-71.7</v>
       </c>
       <c r="F31">
-        <v>66.11999999999999</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="G31">
         <v>55.2</v>
@@ -3823,28 +3823,28 @@
         <v>16.29</v>
       </c>
       <c r="M31">
-        <v>3.821736</v>
+        <v>3.95352</v>
       </c>
       <c r="N31">
-        <v>12.468264</v>
+        <v>12.33648</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>12.468264</v>
+        <v>12.33648</v>
       </c>
       <c r="Q31">
-        <v>27.678264</v>
+        <v>27.54648</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09038134961783917</v>
+        <v>0.09101822604095117</v>
       </c>
       <c r="T31">
-        <v>0.8689734832740927</v>
+        <v>0.8813873901780085</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.262460829319451</v>
+        <v>4.12037880167547</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08105275822866581</v>
+        <v>0.08225775822866579</v>
       </c>
       <c r="C32">
-        <v>177.906724197335</v>
+        <v>169.3102743154352</v>
       </c>
       <c r="D32">
-        <v>191.106724197335</v>
+        <v>184.7902743154352</v>
       </c>
       <c r="E32">
-        <v>-71.7</v>
+        <v>-69.42</v>
       </c>
       <c r="F32">
-        <v>68.39999999999999</v>
+        <v>70.67999999999999</v>
       </c>
       <c r="G32">
         <v>55.2</v>
@@ -3905,45 +3905,45 @@
         <v>16.29</v>
       </c>
       <c r="M32">
-        <v>3.95352</v>
+        <v>4.332684</v>
       </c>
       <c r="N32">
-        <v>12.33648</v>
+        <v>11.957316</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>12.33648</v>
+        <v>11.957316</v>
       </c>
       <c r="Q32">
-        <v>27.54648</v>
+        <v>27.167316</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09101822604095117</v>
+        <v>0.09167356265024031</v>
       </c>
       <c r="T32">
-        <v>0.8813873901780085</v>
+        <v>0.8941611204704434</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.12037880167547</v>
+        <v>3.759794159924887</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08225775822866579</v>
+        <v>0.08241275822866581</v>
       </c>
       <c r="C33">
-        <v>169.3102743154352</v>
+        <v>166.2479652542056</v>
       </c>
       <c r="D33">
-        <v>184.7902743154352</v>
+        <v>184.0079652542056</v>
       </c>
       <c r="E33">
-        <v>-69.42</v>
+        <v>-67.13999999999999</v>
       </c>
       <c r="F33">
-        <v>70.67999999999999</v>
+        <v>72.96000000000001</v>
       </c>
       <c r="G33">
         <v>55.2</v>
@@ -3987,28 +3987,28 @@
         <v>16.29</v>
       </c>
       <c r="M33">
-        <v>4.332684</v>
+        <v>4.472448000000001</v>
       </c>
       <c r="N33">
-        <v>11.957316</v>
+        <v>11.817552</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>11.957316</v>
+        <v>11.817552</v>
       </c>
       <c r="Q33">
-        <v>27.167316</v>
+        <v>27.027552</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09167356265024031</v>
+        <v>0.09234817386568503</v>
       </c>
       <c r="T33">
-        <v>0.8941611204704434</v>
+        <v>0.9073105487126558</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.759794159924887</v>
+        <v>3.642300592427234</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08241275822866581</v>
+        <v>0.08256775822866581</v>
       </c>
       <c r="C34">
-        <v>166.2479652542056</v>
+        <v>163.1922520753649</v>
       </c>
       <c r="D34">
-        <v>184.0079652542056</v>
+        <v>183.232252075365</v>
       </c>
       <c r="E34">
-        <v>-67.13999999999999</v>
+        <v>-64.85999999999999</v>
       </c>
       <c r="F34">
-        <v>72.96000000000001</v>
+        <v>75.24000000000001</v>
       </c>
       <c r="G34">
         <v>55.2</v>
@@ -4069,28 +4069,28 @@
         <v>16.29</v>
       </c>
       <c r="M34">
-        <v>4.472448000000001</v>
+        <v>4.612212</v>
       </c>
       <c r="N34">
-        <v>11.817552</v>
+        <v>11.677788</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>11.817552</v>
+        <v>11.677788</v>
       </c>
       <c r="Q34">
-        <v>27.027552</v>
+        <v>26.887788</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09234817386568503</v>
+        <v>0.09304292272935197</v>
       </c>
       <c r="T34">
-        <v>0.9073105487126558</v>
+        <v>0.9208524972009045</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.642300592427234</v>
+        <v>3.531927847202166</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08256775822866581</v>
+        <v>0.08367475822866581</v>
       </c>
       <c r="C35">
-        <v>163.1922520753649</v>
+        <v>155.5567564224869</v>
       </c>
       <c r="D35">
-        <v>183.232252075365</v>
+        <v>177.8767564224869</v>
       </c>
       <c r="E35">
-        <v>-64.85999999999999</v>
+        <v>-62.57999999999998</v>
       </c>
       <c r="F35">
-        <v>75.24000000000001</v>
+        <v>77.52000000000001</v>
       </c>
       <c r="G35">
         <v>55.2</v>
@@ -4151,45 +4151,45 @@
         <v>16.29</v>
       </c>
       <c r="M35">
-        <v>4.612212</v>
+        <v>4.969032000000001</v>
       </c>
       <c r="N35">
-        <v>11.677788</v>
+        <v>11.320968</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>11.677788</v>
+        <v>11.320968</v>
       </c>
       <c r="Q35">
-        <v>26.887788</v>
+        <v>26.53096799999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09304292272935197</v>
+        <v>0.09375872458888759</v>
       </c>
       <c r="T35">
-        <v>0.9208524972009045</v>
+        <v>0.9348048077645544</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.531927847202166</v>
+        <v>3.278304506793273</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08367475822866581</v>
+        <v>0.08385775822866581</v>
       </c>
       <c r="C36">
-        <v>155.5567564224869</v>
+        <v>152.4214394532178</v>
       </c>
       <c r="D36">
-        <v>177.8767564224869</v>
+        <v>177.0214394532179</v>
       </c>
       <c r="E36">
-        <v>-62.57999999999998</v>
+        <v>-60.29999999999998</v>
       </c>
       <c r="F36">
-        <v>77.52000000000001</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="G36">
         <v>55.2</v>
@@ -4233,28 +4233,28 @@
         <v>16.29</v>
       </c>
       <c r="M36">
-        <v>4.969032000000001</v>
+        <v>5.115180000000001</v>
       </c>
       <c r="N36">
-        <v>11.320968</v>
+        <v>11.17482</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>11.320968</v>
+        <v>11.17482</v>
       </c>
       <c r="Q36">
-        <v>26.53096799999999</v>
+        <v>26.38482</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09375872458888759</v>
+        <v>0.09449655112102434</v>
       </c>
       <c r="T36">
-        <v>0.9348048077645544</v>
+        <v>0.9491864201917015</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.278304506793273</v>
+        <v>3.184638663742037</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08385775822866581</v>
+        <v>0.08404075822866582</v>
       </c>
       <c r="C37">
-        <v>152.4214394532178</v>
+        <v>149.2943086712854</v>
       </c>
       <c r="D37">
-        <v>177.0214394532179</v>
+        <v>176.1743086712854</v>
       </c>
       <c r="E37">
-        <v>-60.29999999999998</v>
+        <v>-58.01999999999998</v>
       </c>
       <c r="F37">
-        <v>79.80000000000001</v>
+        <v>82.08000000000001</v>
       </c>
       <c r="G37">
         <v>55.2</v>
@@ -4315,28 +4315,28 @@
         <v>16.29</v>
       </c>
       <c r="M37">
-        <v>5.115180000000001</v>
+        <v>5.261328000000002</v>
       </c>
       <c r="N37">
-        <v>11.17482</v>
+        <v>11.028672</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>11.17482</v>
+        <v>11.028672</v>
       </c>
       <c r="Q37">
-        <v>26.38482</v>
+        <v>26.23867199999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09449655112102434</v>
+        <v>0.09525743473229034</v>
       </c>
       <c r="T37">
-        <v>0.9491864201917015</v>
+        <v>0.9640174580071967</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.184638663742037</v>
+        <v>3.096176478638092</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08404075822866583</v>
+        <v>0.08422375822866582</v>
       </c>
       <c r="C38">
-        <v>149.2943086712853</v>
+        <v>146.1752471121588</v>
       </c>
       <c r="D38">
-        <v>176.1743086712853</v>
+        <v>175.3352471121588</v>
       </c>
       <c r="E38">
-        <v>-58.02</v>
+        <v>-55.73999999999999</v>
       </c>
       <c r="F38">
-        <v>82.08</v>
+        <v>84.36</v>
       </c>
       <c r="G38">
         <v>55.2</v>
@@ -4397,28 +4397,28 @@
         <v>16.29</v>
       </c>
       <c r="M38">
-        <v>5.261328000000001</v>
+        <v>5.407476</v>
       </c>
       <c r="N38">
-        <v>11.028672</v>
+        <v>10.882524</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>11.028672</v>
+        <v>10.882524</v>
       </c>
       <c r="Q38">
-        <v>26.238672</v>
+        <v>26.092524</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09525743473229034</v>
+        <v>0.09604247337883462</v>
       </c>
       <c r="T38">
-        <v>0.9640174580071967</v>
+        <v>0.9793193224200095</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.096176478638093</v>
+        <v>3.012496033269496</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08422375822866582</v>
+        <v>0.08737075822866582</v>
       </c>
       <c r="C39">
-        <v>146.1752471121588</v>
+        <v>130.6219741151445</v>
       </c>
       <c r="D39">
-        <v>175.3352471121588</v>
+        <v>162.0619741151445</v>
       </c>
       <c r="E39">
-        <v>-55.73999999999999</v>
+        <v>-53.45999999999999</v>
       </c>
       <c r="F39">
-        <v>84.36</v>
+        <v>86.64</v>
       </c>
       <c r="G39">
         <v>55.2</v>
@@ -4479,45 +4479,45 @@
         <v>16.29</v>
       </c>
       <c r="M39">
-        <v>5.407476</v>
+        <v>6.229416000000001</v>
       </c>
       <c r="N39">
-        <v>10.882524</v>
+        <v>10.060584</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>10.882524</v>
+        <v>10.060584</v>
       </c>
       <c r="Q39">
-        <v>26.092524</v>
+        <v>25.270584</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09604247337883462</v>
+        <v>0.09685283585268679</v>
       </c>
       <c r="T39">
-        <v>0.9793193224200095</v>
+        <v>0.9951147953622675</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.012496033269496</v>
+        <v>2.615012386393845</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08737075822866582</v>
+        <v>0.08763175822866581</v>
       </c>
       <c r="C40">
-        <v>130.6219741151445</v>
+        <v>127.3308242846058</v>
       </c>
       <c r="D40">
-        <v>162.0619741151445</v>
+        <v>161.0508242846057</v>
       </c>
       <c r="E40">
-        <v>-53.45999999999999</v>
+        <v>-51.17999999999999</v>
       </c>
       <c r="F40">
-        <v>86.64</v>
+        <v>88.92</v>
       </c>
       <c r="G40">
         <v>55.2</v>
@@ -4561,28 +4561,28 @@
         <v>16.29</v>
       </c>
       <c r="M40">
-        <v>6.229416000000001</v>
+        <v>6.393348</v>
       </c>
       <c r="N40">
-        <v>10.060584</v>
+        <v>9.896652</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>10.060584</v>
+        <v>9.896652</v>
       </c>
       <c r="Q40">
-        <v>25.270584</v>
+        <v>25.106652</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09685283585268679</v>
+        <v>0.09768976758797675</v>
       </c>
       <c r="T40">
-        <v>0.9951147953622675</v>
+        <v>1.011428152663288</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.615012386393845</v>
+        <v>2.547960786742721</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08763175822866581</v>
+        <v>0.08945275822866582</v>
       </c>
       <c r="C41">
-        <v>127.3308242846058</v>
+        <v>118.3324962127342</v>
       </c>
       <c r="D41">
-        <v>161.0508242846057</v>
+        <v>154.3324962127342</v>
       </c>
       <c r="E41">
-        <v>-51.17999999999999</v>
+        <v>-48.89999999999999</v>
       </c>
       <c r="F41">
-        <v>88.92</v>
+        <v>91.2</v>
       </c>
       <c r="G41">
         <v>55.2</v>
@@ -4643,45 +4643,45 @@
         <v>16.29</v>
       </c>
       <c r="M41">
-        <v>6.393348</v>
+        <v>6.912960000000001</v>
       </c>
       <c r="N41">
-        <v>9.896652</v>
+        <v>9.377039999999997</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>9.896652</v>
+        <v>9.377039999999997</v>
       </c>
       <c r="Q41">
-        <v>25.106652</v>
+        <v>24.58703999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09768976758797675</v>
+        <v>0.09855459704777636</v>
       </c>
       <c r="T41">
-        <v>1.011428152663288</v>
+        <v>1.02828528854101</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.547960786742721</v>
+        <v>2.356443549507012</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08945275822866582</v>
+        <v>0.08975275822866581</v>
       </c>
       <c r="C42">
-        <v>118.3324962127342</v>
+        <v>114.9990981842659</v>
       </c>
       <c r="D42">
-        <v>154.3324962127342</v>
+        <v>153.2790981842659</v>
       </c>
       <c r="E42">
-        <v>-48.89999999999999</v>
+        <v>-46.61999999999999</v>
       </c>
       <c r="F42">
-        <v>91.2</v>
+        <v>93.48</v>
       </c>
       <c r="G42">
         <v>55.2</v>
@@ -4725,28 +4725,28 @@
         <v>16.29</v>
       </c>
       <c r="M42">
-        <v>6.912960000000001</v>
+        <v>7.085784000000001</v>
       </c>
       <c r="N42">
-        <v>9.377039999999997</v>
+        <v>9.204215999999999</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>9.377039999999997</v>
+        <v>9.204215999999999</v>
       </c>
       <c r="Q42">
-        <v>24.58703999999999</v>
+        <v>24.414216</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09855459704777636</v>
+        <v>0.09944874276045051</v>
       </c>
       <c r="T42">
-        <v>1.02828528854101</v>
+        <v>1.045713852753569</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.356443549507012</v>
+        <v>2.298969316592207</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08975275822866581</v>
+        <v>0.09005275822866582</v>
       </c>
       <c r="C43">
-        <v>114.9990981842659</v>
+        <v>111.6799826286282</v>
       </c>
       <c r="D43">
-        <v>153.2790981842659</v>
+        <v>152.2399826286282</v>
       </c>
       <c r="E43">
-        <v>-46.61999999999999</v>
+        <v>-44.33999999999999</v>
       </c>
       <c r="F43">
-        <v>93.48</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="G43">
         <v>55.2</v>
@@ -4807,28 +4807,28 @@
         <v>16.29</v>
       </c>
       <c r="M43">
-        <v>7.085784000000001</v>
+        <v>7.258608000000001</v>
       </c>
       <c r="N43">
-        <v>9.204215999999999</v>
+        <v>9.031391999999999</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>9.204215999999999</v>
+        <v>9.031391999999999</v>
       </c>
       <c r="Q43">
-        <v>24.414216</v>
+        <v>24.241392</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09944874276045051</v>
+        <v>0.1003737210839066</v>
       </c>
       <c r="T43">
-        <v>1.045713852753569</v>
+        <v>1.063743401938976</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.298969316592207</v>
+        <v>2.24423195191144</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09005275822866582</v>
+        <v>0.09035275822866581</v>
       </c>
       <c r="C44">
-        <v>111.6799826286282</v>
+        <v>108.3748610288795</v>
       </c>
       <c r="D44">
-        <v>152.2399826286282</v>
+        <v>151.2148610288795</v>
       </c>
       <c r="E44">
-        <v>-44.34</v>
+        <v>-42.06</v>
       </c>
       <c r="F44">
-        <v>95.75999999999999</v>
+        <v>98.03999999999999</v>
       </c>
       <c r="G44">
         <v>55.2</v>
@@ -4889,28 +4889,28 @@
         <v>16.29</v>
       </c>
       <c r="M44">
-        <v>7.258608</v>
+        <v>7.431432</v>
       </c>
       <c r="N44">
-        <v>9.031392</v>
+        <v>8.858567999999998</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>9.031392</v>
+        <v>8.858567999999998</v>
       </c>
       <c r="Q44">
-        <v>24.241392</v>
+        <v>24.068568</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1003737210839066</v>
+        <v>0.101331154787133</v>
       </c>
       <c r="T44">
-        <v>1.063743401938976</v>
+        <v>1.082405566885273</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.244231951911441</v>
+        <v>2.192040511169314</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09035275822866581</v>
+        <v>0.09065275822866582</v>
       </c>
       <c r="C45">
-        <v>108.3748610288795</v>
+        <v>105.0834525871201</v>
       </c>
       <c r="D45">
-        <v>151.2148610288795</v>
+        <v>150.2034525871201</v>
       </c>
       <c r="E45">
-        <v>-42.06</v>
+        <v>-39.77999999999999</v>
       </c>
       <c r="F45">
-        <v>98.03999999999999</v>
+        <v>100.32</v>
       </c>
       <c r="G45">
         <v>55.2</v>
@@ -4971,28 +4971,28 @@
         <v>16.29</v>
       </c>
       <c r="M45">
-        <v>7.431432</v>
+        <v>7.604256000000001</v>
       </c>
       <c r="N45">
-        <v>8.858567999999998</v>
+        <v>8.685743999999998</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>8.858567999999998</v>
+        <v>8.685743999999998</v>
       </c>
       <c r="Q45">
-        <v>24.068568</v>
+        <v>23.895744</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.101331154787133</v>
+        <v>0.102322782551189</v>
       </c>
       <c r="T45">
-        <v>1.082405566885273</v>
+        <v>1.101734237722511</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.192040511169314</v>
+        <v>2.142221408642738</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09065275822866582</v>
+        <v>0.0909527582286658</v>
       </c>
       <c r="C46">
-        <v>105.0834525871201</v>
+        <v>101.8054839680618</v>
       </c>
       <c r="D46">
-        <v>150.2034525871201</v>
+        <v>149.2054839680619</v>
       </c>
       <c r="E46">
-        <v>-39.77999999999999</v>
+        <v>-37.49999999999999</v>
       </c>
       <c r="F46">
-        <v>100.32</v>
+        <v>102.6</v>
       </c>
       <c r="G46">
         <v>55.2</v>
@@ -5053,28 +5053,28 @@
         <v>16.29</v>
       </c>
       <c r="M46">
-        <v>7.604256000000001</v>
+        <v>7.777080000000002</v>
       </c>
       <c r="N46">
-        <v>8.685743999999998</v>
+        <v>8.512919999999998</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>8.685743999999998</v>
+        <v>8.512919999999998</v>
       </c>
       <c r="Q46">
-        <v>23.895744</v>
+        <v>23.72291999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.102322782551189</v>
+        <v>0.1033504695066651</v>
       </c>
       <c r="T46">
-        <v>1.101734237722511</v>
+        <v>1.121765769317465</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.142221408642738</v>
+        <v>2.094616488450677</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0909527582286658</v>
+        <v>0.09125275822866583</v>
       </c>
       <c r="C47">
-        <v>101.8054839680618</v>
+        <v>98.54068905275146</v>
       </c>
       <c r="D47">
-        <v>149.2054839680619</v>
+        <v>148.2206890527515</v>
       </c>
       <c r="E47">
-        <v>-37.49999999999999</v>
+        <v>-35.21999999999998</v>
       </c>
       <c r="F47">
-        <v>102.6</v>
+        <v>104.88</v>
       </c>
       <c r="G47">
         <v>55.2</v>
@@ -5135,28 +5135,28 @@
         <v>16.29</v>
       </c>
       <c r="M47">
-        <v>7.777080000000002</v>
+        <v>7.949904000000001</v>
       </c>
       <c r="N47">
-        <v>8.512919999999998</v>
+        <v>8.340095999999999</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>8.512919999999998</v>
+        <v>8.340095999999999</v>
       </c>
       <c r="Q47">
-        <v>23.72291999999999</v>
+        <v>23.550096</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1033504695066651</v>
+        <v>0.1044162189419737</v>
       </c>
       <c r="T47">
-        <v>1.121765769317465</v>
+        <v>1.142539209490011</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.094616488450677</v>
+        <v>2.049081347397403</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09125275822866583</v>
+        <v>0.09155275822866582</v>
       </c>
       <c r="C48">
-        <v>98.54068905275146</v>
+        <v>95.28880870198465</v>
       </c>
       <c r="D48">
-        <v>148.2206890527515</v>
+        <v>147.2488087019847</v>
       </c>
       <c r="E48">
-        <v>-35.21999999999998</v>
+        <v>-32.93999999999998</v>
       </c>
       <c r="F48">
-        <v>104.88</v>
+        <v>107.16</v>
       </c>
       <c r="G48">
         <v>55.2</v>
@@ -5217,28 +5217,28 @@
         <v>16.29</v>
       </c>
       <c r="M48">
-        <v>7.949904000000001</v>
+        <v>8.122728000000002</v>
       </c>
       <c r="N48">
-        <v>8.340095999999999</v>
+        <v>8.167271999999997</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>8.340095999999999</v>
+        <v>8.167271999999997</v>
       </c>
       <c r="Q48">
-        <v>23.550096</v>
+        <v>23.377272</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1044162189419737</v>
+        <v>0.1055221853371053</v>
       </c>
       <c r="T48">
-        <v>1.142539209490011</v>
+        <v>1.164096553065294</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.049081347397403</v>
+        <v>2.005483871920862</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09155275822866582</v>
+        <v>0.09866875822866582</v>
       </c>
       <c r="C49">
-        <v>95.28880870198465</v>
+        <v>73.18949465281931</v>
       </c>
       <c r="D49">
-        <v>147.2488087019847</v>
+        <v>127.4294946528193</v>
       </c>
       <c r="E49">
-        <v>-32.93999999999998</v>
+        <v>-30.65999999999998</v>
       </c>
       <c r="F49">
-        <v>107.16</v>
+        <v>109.44</v>
       </c>
       <c r="G49">
         <v>55.2</v>
@@ -5299,45 +5299,45 @@
         <v>16.29</v>
       </c>
       <c r="M49">
-        <v>8.122728000000002</v>
+        <v>9.849600000000001</v>
       </c>
       <c r="N49">
-        <v>8.167271999999997</v>
+        <v>6.440399999999999</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>8.167271999999997</v>
+        <v>6.440399999999999</v>
       </c>
       <c r="Q49">
-        <v>23.377272</v>
+        <v>21.6504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1055221853371053</v>
+        <v>0.1066706889012804</v>
       </c>
       <c r="T49">
-        <v>1.164096553065294</v>
+        <v>1.186483025239627</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.005483871920862</v>
+        <v>1.653874269005848</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0986687582286658</v>
+        <v>0.09911075822866582</v>
       </c>
       <c r="C50">
-        <v>73.18949465281935</v>
+        <v>69.85297550906685</v>
       </c>
       <c r="D50">
-        <v>127.4294946528194</v>
+        <v>126.3729755090668</v>
       </c>
       <c r="E50">
-        <v>-30.66</v>
+        <v>-28.38</v>
       </c>
       <c r="F50">
-        <v>109.44</v>
+        <v>111.72</v>
       </c>
       <c r="G50">
         <v>55.2</v>
@@ -5381,28 +5381,28 @@
         <v>16.29</v>
       </c>
       <c r="M50">
-        <v>9.849599999999999</v>
+        <v>10.0548</v>
       </c>
       <c r="N50">
-        <v>6.4404</v>
+        <v>6.235199999999999</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>6.4404</v>
+        <v>6.235199999999999</v>
       </c>
       <c r="Q50">
-        <v>21.6504</v>
+        <v>21.4452</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1066706889012804</v>
+        <v>0.1078642318209134</v>
       </c>
       <c r="T50">
-        <v>1.186483025239627</v>
+        <v>1.209747398283541</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.653874269005848</v>
+        <v>1.620121732903688</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09911075822866582</v>
+        <v>0.09955275822866581</v>
       </c>
       <c r="C51">
-        <v>69.85297550906685</v>
+        <v>66.53383152807538</v>
       </c>
       <c r="D51">
-        <v>126.3729755090668</v>
+        <v>125.3338315280754</v>
       </c>
       <c r="E51">
-        <v>-28.38</v>
+        <v>-26.09999999999999</v>
       </c>
       <c r="F51">
-        <v>111.72</v>
+        <v>114</v>
       </c>
       <c r="G51">
         <v>55.2</v>
@@ -5463,28 +5463,28 @@
         <v>16.29</v>
       </c>
       <c r="M51">
-        <v>10.0548</v>
+        <v>10.26</v>
       </c>
       <c r="N51">
-        <v>6.235199999999999</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>6.235199999999999</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="Q51">
-        <v>21.4452</v>
+        <v>21.24</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1078642318209134</v>
+        <v>0.1091055164573316</v>
       </c>
       <c r="T51">
-        <v>1.209747398283541</v>
+        <v>1.233942346249212</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.620121732903688</v>
+        <v>1.587719298245614</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09955275822866581</v>
+        <v>0.0999947582286658</v>
       </c>
       <c r="C52">
-        <v>66.53383152807538</v>
+        <v>63.23163758633532</v>
       </c>
       <c r="D52">
-        <v>125.3338315280754</v>
+        <v>124.3116375863353</v>
       </c>
       <c r="E52">
-        <v>-26.09999999999999</v>
+        <v>-23.81999999999999</v>
       </c>
       <c r="F52">
-        <v>114</v>
+        <v>116.28</v>
       </c>
       <c r="G52">
         <v>55.2</v>
@@ -5545,28 +5545,28 @@
         <v>16.29</v>
       </c>
       <c r="M52">
-        <v>10.26</v>
+        <v>10.4652</v>
       </c>
       <c r="N52">
-        <v>6.029999999999999</v>
+        <v>5.8248</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>6.029999999999999</v>
+        <v>5.8248</v>
       </c>
       <c r="Q52">
-        <v>21.24</v>
+        <v>21.0348</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1091055164573316</v>
+        <v>0.1103974657727874</v>
       </c>
       <c r="T52">
-        <v>1.233942346249212</v>
+        <v>1.259124843111441</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.587719298245614</v>
+        <v>1.556587547299622</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0999947582286658</v>
+        <v>0.1004367582286658</v>
       </c>
       <c r="C53">
-        <v>63.23163758633532</v>
+        <v>59.94598231697984</v>
       </c>
       <c r="D53">
-        <v>124.3116375863353</v>
+        <v>123.3059823169798</v>
       </c>
       <c r="E53">
-        <v>-23.81999999999999</v>
+        <v>-21.53999999999999</v>
       </c>
       <c r="F53">
-        <v>116.28</v>
+        <v>118.56</v>
       </c>
       <c r="G53">
         <v>55.2</v>
@@ -5627,28 +5627,28 @@
         <v>16.29</v>
       </c>
       <c r="M53">
-        <v>10.4652</v>
+        <v>10.6704</v>
       </c>
       <c r="N53">
-        <v>5.8248</v>
+        <v>5.6196</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>5.8248</v>
+        <v>5.6196</v>
       </c>
       <c r="Q53">
-        <v>21.0348</v>
+        <v>20.8296</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1103974657727874</v>
+        <v>0.1117432463097204</v>
       </c>
       <c r="T53">
-        <v>1.259124843111441</v>
+        <v>1.285356610676262</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.556587547299622</v>
+        <v>1.526653171390014</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1004367582286658</v>
+        <v>0.1309827582286658</v>
       </c>
       <c r="C54">
-        <v>59.94598231697984</v>
+        <v>13.4492345363596</v>
       </c>
       <c r="D54">
-        <v>123.3059823169798</v>
+        <v>79.0892345363596</v>
       </c>
       <c r="E54">
-        <v>-21.53999999999999</v>
+        <v>-19.25999999999999</v>
       </c>
       <c r="F54">
-        <v>118.56</v>
+        <v>120.84</v>
       </c>
       <c r="G54">
         <v>55.2</v>
@@ -5709,45 +5709,45 @@
         <v>16.29</v>
       </c>
       <c r="M54">
-        <v>10.6704</v>
+        <v>17.739312</v>
       </c>
       <c r="N54">
-        <v>5.6196</v>
+        <v>-1.449312000000003</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P54">
-        <v>5.6196</v>
+        <v>-1.449312000000003</v>
       </c>
       <c r="Q54">
-        <v>20.8296</v>
+        <v>13.760688</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1117432463097204</v>
+        <v>0.1131462941035443</v>
       </c>
       <c r="T54">
-        <v>1.285356610676262</v>
+        <v>1.312704623669374</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.526653171390014</v>
+        <v>0.9182994244647141</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1309827582286658</v>
+        <v>0.1319927582286658</v>
       </c>
       <c r="C55">
-        <v>13.4492345363596</v>
+        <v>10.24247307143693</v>
       </c>
       <c r="D55">
-        <v>79.0892345363596</v>
+        <v>78.16247307143693</v>
       </c>
       <c r="E55">
-        <v>-19.25999999999999</v>
+        <v>-16.97999999999999</v>
       </c>
       <c r="F55">
-        <v>120.84</v>
+        <v>123.12</v>
       </c>
       <c r="G55">
         <v>55.2</v>
@@ -5791,28 +5791,28 @@
         <v>16.29</v>
       </c>
       <c r="M55">
-        <v>17.739312</v>
+        <v>18.074016</v>
       </c>
       <c r="N55">
-        <v>-1.449312000000003</v>
+        <v>-1.784016000000005</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-1.449312000000003</v>
+        <v>-1.784016000000005</v>
       </c>
       <c r="Q55">
-        <v>13.760688</v>
+        <v>13.42598399999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1131462941035443</v>
+        <v>0.1146103439753605</v>
       </c>
       <c r="T55">
-        <v>1.312704623669374</v>
+        <v>1.341241680705665</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9182994244647141</v>
+        <v>0.9012938795672194</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1319927582286658</v>
+        <v>0.1330027582286658</v>
       </c>
       <c r="C56">
-        <v>10.24247307143693</v>
+        <v>7.057179484333403</v>
       </c>
       <c r="D56">
-        <v>78.16247307143693</v>
+        <v>77.25717948433341</v>
       </c>
       <c r="E56">
-        <v>-16.97999999999999</v>
+        <v>-14.69999999999999</v>
       </c>
       <c r="F56">
-        <v>123.12</v>
+        <v>125.4</v>
       </c>
       <c r="G56">
         <v>55.2</v>
@@ -5873,28 +5873,28 @@
         <v>16.29</v>
       </c>
       <c r="M56">
-        <v>18.074016</v>
+        <v>18.40872</v>
       </c>
       <c r="N56">
-        <v>-1.784016000000005</v>
+        <v>-2.118720000000003</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-1.784016000000005</v>
+        <v>-2.118720000000003</v>
       </c>
       <c r="Q56">
-        <v>13.42598399999999</v>
+        <v>13.09128</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1146103439753605</v>
+        <v>0.1161394627303685</v>
       </c>
       <c r="T56">
-        <v>1.341241680705665</v>
+        <v>1.371047051388013</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9012938795672194</v>
+        <v>0.8849067181205427</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1330027582286658</v>
+        <v>0.1340127582286658</v>
       </c>
       <c r="C57">
-        <v>7.057179484333403</v>
+        <v>3.89261637978899</v>
       </c>
       <c r="D57">
-        <v>77.25717948433341</v>
+        <v>76.37261637978898</v>
       </c>
       <c r="E57">
-        <v>-14.69999999999999</v>
+        <v>-12.41999999999999</v>
       </c>
       <c r="F57">
-        <v>125.4</v>
+        <v>127.68</v>
       </c>
       <c r="G57">
         <v>55.2</v>
@@ -5955,28 +5955,28 @@
         <v>16.29</v>
       </c>
       <c r="M57">
-        <v>18.40872</v>
+        <v>18.743424</v>
       </c>
       <c r="N57">
-        <v>-2.118720000000003</v>
+        <v>-2.453424000000005</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-2.118720000000003</v>
+        <v>-2.453424000000005</v>
       </c>
       <c r="Q57">
-        <v>13.09128</v>
+        <v>12.75657599999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1161394627303685</v>
+        <v>0.1177380868833314</v>
       </c>
       <c r="T57">
-        <v>1.371047051388013</v>
+        <v>1.402207211646832</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8849067181205427</v>
+        <v>0.8691048124398186</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1340127582286658</v>
+        <v>0.1350227582286658</v>
       </c>
       <c r="C58">
-        <v>3.89261637978899</v>
+        <v>0.7480797517473263</v>
       </c>
       <c r="D58">
-        <v>76.37261637978898</v>
+        <v>75.50807975174732</v>
       </c>
       <c r="E58">
-        <v>-12.41999999999999</v>
+        <v>-10.13999999999999</v>
       </c>
       <c r="F58">
-        <v>127.68</v>
+        <v>129.96</v>
       </c>
       <c r="G58">
         <v>55.2</v>
@@ -6037,28 +6037,28 @@
         <v>16.29</v>
       </c>
       <c r="M58">
-        <v>18.743424</v>
+        <v>19.078128</v>
       </c>
       <c r="N58">
-        <v>-2.453424000000005</v>
+        <v>-2.788128000000004</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-2.453424000000005</v>
+        <v>-2.788128000000004</v>
       </c>
       <c r="Q58">
-        <v>12.75657599999999</v>
+        <v>12.421872</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1177380868833314</v>
+        <v>0.1194110656480601</v>
       </c>
       <c r="T58">
-        <v>1.402207211646832</v>
+        <v>1.43481668168513</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8691048124398186</v>
+        <v>0.8538573595899973</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1350227582286658</v>
+        <v>0.1360327582286658</v>
       </c>
       <c r="C59">
-        <v>0.7480797517473263</v>
+        <v>-2.377102885316731</v>
       </c>
       <c r="D59">
-        <v>75.50807975174732</v>
+        <v>74.66289711468326</v>
       </c>
       <c r="E59">
-        <v>-10.13999999999999</v>
+        <v>-7.859999999999985</v>
       </c>
       <c r="F59">
-        <v>129.96</v>
+        <v>132.24</v>
       </c>
       <c r="G59">
         <v>55.2</v>
@@ -6119,28 +6119,28 @@
         <v>16.29</v>
       </c>
       <c r="M59">
-        <v>19.078128</v>
+        <v>19.412832</v>
       </c>
       <c r="N59">
-        <v>-2.788128000000004</v>
+        <v>-3.122832000000002</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-2.788128000000004</v>
+        <v>-3.122832000000002</v>
       </c>
       <c r="Q59">
-        <v>12.421872</v>
+        <v>12.087168</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1194110656480601</v>
+        <v>0.1211637100682519</v>
       </c>
       <c r="T59">
-        <v>1.43481668168513</v>
+        <v>1.468978983630014</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8538573595899973</v>
+        <v>0.8391356809763768</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1360327582286658</v>
+        <v>0.1370427582286658</v>
       </c>
       <c r="C60">
-        <v>-2.377102885316702</v>
+        <v>-5.483574240959456</v>
       </c>
       <c r="D60">
-        <v>74.66289711468328</v>
+        <v>73.83642575904052</v>
       </c>
       <c r="E60">
-        <v>-7.860000000000014</v>
+        <v>-5.580000000000013</v>
       </c>
       <c r="F60">
-        <v>132.24</v>
+        <v>134.52</v>
       </c>
       <c r="G60">
         <v>55.2</v>
@@ -6201,28 +6201,28 @@
         <v>16.29</v>
       </c>
       <c r="M60">
-        <v>19.412832</v>
+        <v>19.747536</v>
       </c>
       <c r="N60">
-        <v>-3.122831999999999</v>
+        <v>-3.457536000000001</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-3.122831999999999</v>
+        <v>-3.457536000000001</v>
       </c>
       <c r="Q60">
-        <v>12.087168</v>
+        <v>11.752464</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1211637100682519</v>
+        <v>0.1230018493382093</v>
       </c>
       <c r="T60">
-        <v>1.468978983630014</v>
+        <v>1.504807739328307</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8391356809763769</v>
+        <v>0.8249130423157602</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1370427582286658</v>
+        <v>0.1380527582286658</v>
       </c>
       <c r="C61">
-        <v>-5.483574240959456</v>
+        <v>-8.571948878732172</v>
       </c>
       <c r="D61">
-        <v>73.83642575904052</v>
+        <v>73.02805112126782</v>
       </c>
       <c r="E61">
-        <v>-5.580000000000013</v>
+        <v>-3.300000000000011</v>
       </c>
       <c r="F61">
-        <v>134.52</v>
+        <v>136.8</v>
       </c>
       <c r="G61">
         <v>55.2</v>
@@ -6283,28 +6283,28 @@
         <v>16.29</v>
       </c>
       <c r="M61">
-        <v>19.747536</v>
+        <v>20.08224</v>
       </c>
       <c r="N61">
-        <v>-3.457536000000001</v>
+        <v>-3.79224</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-3.457536000000001</v>
+        <v>-3.79224</v>
       </c>
       <c r="Q61">
-        <v>11.752464</v>
+        <v>11.41776</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1230018493382093</v>
+        <v>0.1249318955716645</v>
       </c>
       <c r="T61">
-        <v>1.504807739328307</v>
+        <v>1.542427932811515</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8249130423157602</v>
+        <v>0.8111644916104976</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1380527582286658</v>
+        <v>0.1720027582286658</v>
       </c>
       <c r="C62">
-        <v>-8.571948878732172</v>
+        <v>-30.49733833269967</v>
       </c>
       <c r="D62">
-        <v>73.02805112126782</v>
+        <v>53.38266166730031</v>
       </c>
       <c r="E62">
-        <v>-3.300000000000011</v>
+        <v>-1.02000000000001</v>
       </c>
       <c r="F62">
-        <v>136.8</v>
+        <v>139.08</v>
       </c>
       <c r="G62">
         <v>55.2</v>
@@ -6365,45 +6365,45 @@
         <v>16.29</v>
       </c>
       <c r="M62">
-        <v>20.08224</v>
+        <v>27.927264</v>
       </c>
       <c r="N62">
-        <v>-3.79224</v>
+        <v>-11.637264</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-3.79224</v>
+        <v>-11.637264</v>
       </c>
       <c r="Q62">
-        <v>11.41776</v>
+        <v>3.572736000000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1249318955716645</v>
+        <v>0.1269609185350405</v>
       </c>
       <c r="T62">
-        <v>1.542427932811515</v>
+        <v>1.581977366986169</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8111644916104976</v>
+        <v>0.5833009635315511</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1720027582286658</v>
+        <v>0.1735527582286658</v>
       </c>
       <c r="C63">
-        <v>-30.49733833269967</v>
+        <v>-33.42502004800333</v>
       </c>
       <c r="D63">
-        <v>53.38266166730031</v>
+        <v>52.73497995199665</v>
       </c>
       <c r="E63">
-        <v>-1.02000000000001</v>
+        <v>1.259999999999991</v>
       </c>
       <c r="F63">
-        <v>139.08</v>
+        <v>141.36</v>
       </c>
       <c r="G63">
         <v>55.2</v>
@@ -6447,28 +6447,28 @@
         <v>16.29</v>
       </c>
       <c r="M63">
-        <v>27.927264</v>
+        <v>28.385088</v>
       </c>
       <c r="N63">
-        <v>-11.637264</v>
+        <v>-12.095088</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-11.637264</v>
+        <v>-12.095088</v>
       </c>
       <c r="Q63">
-        <v>3.572736000000001</v>
+        <v>3.114911999999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1269609185350405</v>
+        <v>0.1290967321806995</v>
       </c>
       <c r="T63">
-        <v>1.581977366986169</v>
+        <v>1.62360835032791</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5833009635315511</v>
+        <v>0.5738928834745906</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1735527582286658</v>
+        <v>0.1751027582286658</v>
       </c>
       <c r="C64">
-        <v>-33.42502004800333</v>
+        <v>-36.33717376262901</v>
       </c>
       <c r="D64">
-        <v>52.73497995199665</v>
+        <v>52.102826237371</v>
       </c>
       <c r="E64">
-        <v>1.259999999999991</v>
+        <v>3.54000000000002</v>
       </c>
       <c r="F64">
-        <v>141.36</v>
+        <v>143.64</v>
       </c>
       <c r="G64">
         <v>55.2</v>
@@ -6529,28 +6529,28 @@
         <v>16.29</v>
       </c>
       <c r="M64">
-        <v>28.385088</v>
+        <v>28.84291200000001</v>
       </c>
       <c r="N64">
-        <v>-12.095088</v>
+        <v>-12.55291200000001</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-12.095088</v>
+        <v>-12.55291200000001</v>
       </c>
       <c r="Q64">
-        <v>3.114911999999999</v>
+        <v>2.657087999999993</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1290967321806995</v>
+        <v>0.1313479952126103</v>
       </c>
       <c r="T64">
-        <v>1.62360835032791</v>
+        <v>1.667489657093529</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5738928834745906</v>
+        <v>0.5647834726257874</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1751027582286658</v>
+        <v>0.1766527582286658</v>
       </c>
       <c r="C65">
-        <v>-36.33717376262901</v>
+        <v>-39.23435128155299</v>
       </c>
       <c r="D65">
-        <v>52.102826237371</v>
+        <v>51.48564871844703</v>
       </c>
       <c r="E65">
-        <v>3.54000000000002</v>
+        <v>5.820000000000022</v>
       </c>
       <c r="F65">
-        <v>143.64</v>
+        <v>145.92</v>
       </c>
       <c r="G65">
         <v>55.2</v>
@@ -6611,28 +6611,28 @@
         <v>16.29</v>
       </c>
       <c r="M65">
-        <v>28.84291200000001</v>
+        <v>29.300736</v>
       </c>
       <c r="N65">
-        <v>-12.55291200000001</v>
+        <v>-13.010736</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-12.55291200000001</v>
+        <v>-13.010736</v>
       </c>
       <c r="Q65">
-        <v>2.657087999999993</v>
+        <v>2.199263999999994</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1313479952126103</v>
+        <v>0.1337243284129606</v>
       </c>
       <c r="T65">
-        <v>1.667489657093529</v>
+        <v>1.713808814235016</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5647834726257874</v>
+        <v>0.5559587308660096</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1766527582286658</v>
+        <v>0.1782027582286658</v>
       </c>
       <c r="C66">
-        <v>-39.23435128155299</v>
+        <v>-42.11707857047978</v>
       </c>
       <c r="D66">
-        <v>51.48564871844703</v>
+        <v>50.88292142952024</v>
       </c>
       <c r="E66">
-        <v>5.820000000000022</v>
+        <v>8.100000000000023</v>
       </c>
       <c r="F66">
-        <v>145.92</v>
+        <v>148.2</v>
       </c>
       <c r="G66">
         <v>55.2</v>
@@ -6693,28 +6693,28 @@
         <v>16.29</v>
       </c>
       <c r="M66">
-        <v>29.300736</v>
+        <v>29.75856</v>
       </c>
       <c r="N66">
-        <v>-13.010736</v>
+        <v>-13.46856</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-13.010736</v>
+        <v>-13.46856</v>
       </c>
       <c r="Q66">
-        <v>2.199263999999994</v>
+        <v>1.741439999999995</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1337243284129606</v>
+        <v>0.1362364520819023</v>
       </c>
       <c r="T66">
-        <v>1.713808814235016</v>
+        <v>1.762774780356017</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5559587308660096</v>
+        <v>0.5474055196219172</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1782027582286658</v>
+        <v>0.1797527582286658</v>
       </c>
       <c r="C67">
-        <v>-42.11707857047978</v>
+        <v>-44.98585725080468</v>
       </c>
       <c r="D67">
-        <v>50.88292142952024</v>
+        <v>50.29414274919532</v>
       </c>
       <c r="E67">
-        <v>8.100000000000023</v>
+        <v>10.38000000000002</v>
       </c>
       <c r="F67">
-        <v>148.2</v>
+        <v>150.48</v>
       </c>
       <c r="G67">
         <v>55.2</v>
@@ -6775,28 +6775,28 @@
         <v>16.29</v>
       </c>
       <c r="M67">
-        <v>29.75856</v>
+        <v>30.21638400000001</v>
       </c>
       <c r="N67">
-        <v>-13.46856</v>
+        <v>-13.92638400000001</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-13.46856</v>
+        <v>-13.92638400000001</v>
       </c>
       <c r="Q67">
-        <v>1.741439999999995</v>
+        <v>1.283615999999993</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1362364520819023</v>
+        <v>0.1388963477313701</v>
       </c>
       <c r="T67">
-        <v>1.762774780356017</v>
+        <v>1.814621097425312</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5474055196219172</v>
+        <v>0.5391114965973426</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1797527582286658</v>
+        <v>0.1813027582286658</v>
       </c>
       <c r="C68">
-        <v>-44.98585725080468</v>
+        <v>-47.84116599197216</v>
       </c>
       <c r="D68">
-        <v>50.29414274919532</v>
+        <v>49.71883400802786</v>
       </c>
       <c r="E68">
-        <v>10.38000000000002</v>
+        <v>12.66000000000003</v>
       </c>
       <c r="F68">
-        <v>150.48</v>
+        <v>152.76</v>
       </c>
       <c r="G68">
         <v>55.2</v>
@@ -6857,28 +6857,28 @@
         <v>16.29</v>
       </c>
       <c r="M68">
-        <v>30.21638400000001</v>
+        <v>30.674208</v>
       </c>
       <c r="N68">
-        <v>-13.92638400000001</v>
+        <v>-14.384208</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-13.92638400000001</v>
+        <v>-14.384208</v>
       </c>
       <c r="Q68">
-        <v>1.283615999999993</v>
+        <v>0.8257919999999945</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1388963477313701</v>
+        <v>0.1417174491777752</v>
       </c>
       <c r="T68">
-        <v>1.814621097425312</v>
+        <v>1.869609615529109</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5391114965973426</v>
+        <v>0.5310650563496211</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1813027582286658</v>
+        <v>0.1828527582286658</v>
       </c>
       <c r="C69">
-        <v>-47.84116599197216</v>
+        <v>-50.68346180935268</v>
       </c>
       <c r="D69">
-        <v>49.71883400802786</v>
+        <v>49.15653819064733</v>
       </c>
       <c r="E69">
-        <v>12.66000000000003</v>
+        <v>14.94000000000003</v>
       </c>
       <c r="F69">
-        <v>152.76</v>
+        <v>155.04</v>
       </c>
       <c r="G69">
         <v>55.2</v>
@@ -6939,28 +6939,28 @@
         <v>16.29</v>
       </c>
       <c r="M69">
-        <v>30.674208</v>
+        <v>31.13203200000001</v>
       </c>
       <c r="N69">
-        <v>-14.384208</v>
+        <v>-14.84203200000001</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-14.384208</v>
+        <v>-14.84203200000001</v>
       </c>
       <c r="Q69">
-        <v>0.8257919999999945</v>
+        <v>0.3679679999999923</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1417174491777752</v>
+        <v>0.1447148694645807</v>
       </c>
       <c r="T69">
-        <v>1.869609615529109</v>
+        <v>1.928034916014394</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5310650563496211</v>
+        <v>0.5232552761091854</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1828527582286658</v>
+        <v>0.1844027582286658</v>
       </c>
       <c r="C70">
-        <v>-50.68346180935268</v>
+        <v>-53.51318127503461</v>
       </c>
       <c r="D70">
-        <v>49.15653819064733</v>
+        <v>48.60681872496541</v>
       </c>
       <c r="E70">
-        <v>14.94000000000003</v>
+        <v>17.22000000000003</v>
       </c>
       <c r="F70">
-        <v>155.04</v>
+        <v>157.32</v>
       </c>
       <c r="G70">
         <v>55.2</v>
@@ -7021,28 +7021,28 @@
         <v>16.29</v>
       </c>
       <c r="M70">
-        <v>31.13203200000001</v>
+        <v>31.589856</v>
       </c>
       <c r="N70">
-        <v>-14.84203200000001</v>
+        <v>-15.29985600000001</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-14.84203200000001</v>
+        <v>-15.29985600000001</v>
       </c>
       <c r="Q70">
-        <v>0.3679679999999923</v>
+        <v>-0.08985600000000638</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1447148694645807</v>
+        <v>0.1479056717053736</v>
       </c>
       <c r="T70">
-        <v>1.928034916014394</v>
+        <v>1.990229590724536</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5232552761091854</v>
+        <v>0.5156718663105015</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1844027582286658</v>
+        <v>0.1859527582286658</v>
       </c>
       <c r="C71">
-        <v>-53.51318127503461</v>
+        <v>-56.33074164827234</v>
       </c>
       <c r="D71">
-        <v>48.60681872496541</v>
+        <v>48.06925835172768</v>
       </c>
       <c r="E71">
-        <v>17.22000000000003</v>
+        <v>19.50000000000003</v>
       </c>
       <c r="F71">
-        <v>157.32</v>
+        <v>159.6</v>
       </c>
       <c r="G71">
         <v>55.2</v>
@@ -7103,28 +7103,28 @@
         <v>16.29</v>
       </c>
       <c r="M71">
-        <v>31.589856</v>
+        <v>32.04768000000001</v>
       </c>
       <c r="N71">
-        <v>-15.29985600000001</v>
+        <v>-15.75768000000001</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-15.29985600000001</v>
+        <v>-15.75768000000001</v>
       </c>
       <c r="Q71">
-        <v>-0.08985600000000638</v>
+        <v>-0.5476800000000086</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1479056717053736</v>
+        <v>0.1513091940955527</v>
       </c>
       <c r="T71">
-        <v>1.990229590724536</v>
+        <v>2.05657057708202</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5156718663105015</v>
+        <v>0.5083051253632087</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1859527582286658</v>
+        <v>0.1875027582286658</v>
       </c>
       <c r="C72">
-        <v>-56.33074164827234</v>
+        <v>-59.13654193174278</v>
       </c>
       <c r="D72">
-        <v>48.06925835172768</v>
+        <v>47.54345806825723</v>
       </c>
       <c r="E72">
-        <v>19.50000000000003</v>
+        <v>21.78000000000003</v>
       </c>
       <c r="F72">
-        <v>159.6</v>
+        <v>161.88</v>
       </c>
       <c r="G72">
         <v>55.2</v>
@@ -7185,28 +7185,28 @@
         <v>16.29</v>
       </c>
       <c r="M72">
-        <v>32.04768000000001</v>
+        <v>32.50550400000001</v>
       </c>
       <c r="N72">
-        <v>-15.75768000000001</v>
+        <v>-16.21550400000001</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-15.75768000000001</v>
+        <v>-16.21550400000001</v>
       </c>
       <c r="Q72">
-        <v>-0.5476800000000086</v>
+        <v>-1.005504000000011</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1513091940955527</v>
+        <v>0.1549474421678132</v>
       </c>
       <c r="T72">
-        <v>2.05657057708202</v>
+        <v>2.127486803877952</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5083051253632087</v>
+        <v>0.501145898245417</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1875027582286658</v>
+        <v>0.2142527582286658</v>
       </c>
       <c r="C73">
-        <v>-59.13654193174274</v>
+        <v>-68.96635896471469</v>
       </c>
       <c r="D73">
-        <v>47.54345806825725</v>
+        <v>39.99364103528531</v>
       </c>
       <c r="E73">
-        <v>21.78</v>
+        <v>24.06</v>
       </c>
       <c r="F73">
-        <v>161.88</v>
+        <v>164.16</v>
       </c>
       <c r="G73">
         <v>55.2</v>
@@ -7267,45 +7267,45 @@
         <v>16.29</v>
       </c>
       <c r="M73">
-        <v>32.505504</v>
+        <v>38.708928</v>
       </c>
       <c r="N73">
-        <v>-16.215504</v>
+        <v>-22.418928</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-16.215504</v>
+        <v>-22.418928</v>
       </c>
       <c r="Q73">
-        <v>-1.005504000000004</v>
+        <v>-7.208928000000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1549474421678131</v>
+        <v>0.1588455651023779</v>
       </c>
       <c r="T73">
-        <v>2.127486803877952</v>
+        <v>2.203468475445021</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5011458982454171</v>
+        <v>0.4208331473297323</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2142527582286658</v>
+        <v>0.2161527582286658</v>
       </c>
       <c r="C74">
-        <v>-68.96635896471469</v>
+        <v>-71.69242111690502</v>
       </c>
       <c r="D74">
-        <v>39.99364103528531</v>
+        <v>39.54757888309498</v>
       </c>
       <c r="E74">
-        <v>24.06</v>
+        <v>26.34</v>
       </c>
       <c r="F74">
-        <v>164.16</v>
+        <v>166.44</v>
       </c>
       <c r="G74">
         <v>55.2</v>
@@ -7349,28 +7349,28 @@
         <v>16.29</v>
       </c>
       <c r="M74">
-        <v>38.708928</v>
+        <v>39.246552</v>
       </c>
       <c r="N74">
-        <v>-22.418928</v>
+        <v>-22.956552</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-22.418928</v>
+        <v>-22.956552</v>
       </c>
       <c r="Q74">
-        <v>-7.208928000000002</v>
+        <v>-7.746552000000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1588455651023779</v>
+        <v>0.1630324378839474</v>
       </c>
       <c r="T74">
-        <v>2.203468475445021</v>
+        <v>2.285078418980022</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4208331473297323</v>
+        <v>0.4150683096950784</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2161527582286658</v>
+        <v>0.2180527582286658</v>
       </c>
       <c r="C75">
-        <v>-71.69242111690502</v>
+        <v>-74.40864286830438</v>
       </c>
       <c r="D75">
-        <v>39.54757888309498</v>
+        <v>39.11135713169561</v>
       </c>
       <c r="E75">
-        <v>26.34</v>
+        <v>28.62</v>
       </c>
       <c r="F75">
-        <v>166.44</v>
+        <v>168.72</v>
       </c>
       <c r="G75">
         <v>55.2</v>
@@ -7431,28 +7431,28 @@
         <v>16.29</v>
       </c>
       <c r="M75">
-        <v>39.246552</v>
+        <v>39.784176</v>
       </c>
       <c r="N75">
-        <v>-22.956552</v>
+        <v>-23.494176</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-22.956552</v>
+        <v>-23.494176</v>
       </c>
       <c r="Q75">
-        <v>-7.746552000000003</v>
+        <v>-8.284176000000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1630324378839474</v>
+        <v>0.1675413778025608</v>
       </c>
       <c r="T75">
-        <v>2.285078418980022</v>
+        <v>2.372966050479253</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4150683096950784</v>
+        <v>0.4094592784829827</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2180527582286658</v>
+        <v>0.2199527582286658</v>
       </c>
       <c r="C76">
-        <v>-74.40864286830438</v>
+        <v>-77.11534629411318</v>
       </c>
       <c r="D76">
-        <v>39.11135713169561</v>
+        <v>38.68465370588682</v>
       </c>
       <c r="E76">
-        <v>28.62</v>
+        <v>30.90000000000001</v>
       </c>
       <c r="F76">
-        <v>168.72</v>
+        <v>171</v>
       </c>
       <c r="G76">
         <v>55.2</v>
@@ -7513,28 +7513,28 @@
         <v>16.29</v>
       </c>
       <c r="M76">
-        <v>39.784176</v>
+        <v>40.3218</v>
       </c>
       <c r="N76">
-        <v>-23.494176</v>
+        <v>-24.0318</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-23.494176</v>
+        <v>-24.0318</v>
       </c>
       <c r="Q76">
-        <v>-8.284176000000004</v>
+        <v>-8.821800000000005</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1675413778025608</v>
+        <v>0.1724110329146633</v>
       </c>
       <c r="T76">
-        <v>2.372966050479253</v>
+        <v>2.467884692498424</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4094592784829827</v>
+        <v>0.403999821436543</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2199527582286658</v>
+        <v>0.2218527582286658</v>
       </c>
       <c r="C77">
-        <v>-77.11534629411318</v>
+        <v>-79.81283956590686</v>
       </c>
       <c r="D77">
-        <v>38.68465370588682</v>
+        <v>38.26716043409314</v>
       </c>
       <c r="E77">
-        <v>30.90000000000001</v>
+        <v>33.18000000000001</v>
       </c>
       <c r="F77">
-        <v>171</v>
+        <v>173.28</v>
       </c>
       <c r="G77">
         <v>55.2</v>
@@ -7595,28 +7595,28 @@
         <v>16.29</v>
       </c>
       <c r="M77">
-        <v>40.3218</v>
+        <v>40.859424</v>
       </c>
       <c r="N77">
-        <v>-24.0318</v>
+        <v>-24.56942400000001</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-24.0318</v>
+        <v>-24.56942400000001</v>
       </c>
       <c r="Q77">
-        <v>-8.821800000000005</v>
+        <v>-9.359424000000006</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1724110329146633</v>
+        <v>0.1776864926194409</v>
       </c>
       <c r="T77">
-        <v>2.467884692498424</v>
+        <v>2.570713221352525</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.403999821436543</v>
+        <v>0.3986840343123779</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2218527582286658</v>
+        <v>0.2237527582286658</v>
       </c>
       <c r="C78">
-        <v>-79.81283956590686</v>
+        <v>-82.50141769388028</v>
       </c>
       <c r="D78">
-        <v>38.26716043409314</v>
+        <v>37.85858230611972</v>
       </c>
       <c r="E78">
-        <v>33.18000000000001</v>
+        <v>35.46000000000001</v>
       </c>
       <c r="F78">
-        <v>173.28</v>
+        <v>175.56</v>
       </c>
       <c r="G78">
         <v>55.2</v>
@@ -7677,28 +7677,28 @@
         <v>16.29</v>
       </c>
       <c r="M78">
-        <v>40.859424</v>
+        <v>41.39704800000001</v>
       </c>
       <c r="N78">
-        <v>-24.56942400000001</v>
+        <v>-25.10704800000001</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-24.56942400000001</v>
+        <v>-25.10704800000001</v>
       </c>
       <c r="Q78">
-        <v>-9.359424000000006</v>
+        <v>-9.897048000000007</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1776864926194409</v>
+        <v>0.1834206879507209</v>
       </c>
       <c r="T78">
-        <v>2.570713221352525</v>
+        <v>2.68248336141133</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3986840343123779</v>
+        <v>0.3935063195810483</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2237527582286658</v>
+        <v>0.2256527582286658</v>
       </c>
       <c r="C79">
-        <v>-82.50141769388028</v>
+        <v>-85.18136322204489</v>
       </c>
       <c r="D79">
-        <v>37.85858230611972</v>
+        <v>37.4586367779551</v>
       </c>
       <c r="E79">
-        <v>35.46000000000001</v>
+        <v>37.74000000000001</v>
       </c>
       <c r="F79">
-        <v>175.56</v>
+        <v>177.84</v>
       </c>
       <c r="G79">
         <v>55.2</v>
@@ -7759,28 +7759,28 @@
         <v>16.29</v>
       </c>
       <c r="M79">
-        <v>41.39704800000001</v>
+        <v>41.934672</v>
       </c>
       <c r="N79">
-        <v>-25.10704800000001</v>
+        <v>-25.644672</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-25.10704800000001</v>
+        <v>-25.644672</v>
       </c>
       <c r="Q79">
-        <v>-9.897048000000007</v>
+        <v>-10.434672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1834206879507209</v>
+        <v>0.1896761737666628</v>
       </c>
       <c r="T79">
-        <v>2.68248336141133</v>
+        <v>2.804414423293664</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3935063195810483</v>
+        <v>0.3884613667659067</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2256527582286658</v>
+        <v>0.2275527582286658</v>
       </c>
       <c r="C80">
-        <v>-85.18136322204489</v>
+        <v>-87.85294687982122</v>
       </c>
       <c r="D80">
-        <v>37.4586367779551</v>
+        <v>37.06705312017879</v>
       </c>
       <c r="E80">
-        <v>37.74000000000001</v>
+        <v>40.02000000000001</v>
       </c>
       <c r="F80">
-        <v>177.84</v>
+        <v>180.12</v>
       </c>
       <c r="G80">
         <v>55.2</v>
@@ -7841,28 +7841,28 @@
         <v>16.29</v>
       </c>
       <c r="M80">
-        <v>41.934672</v>
+        <v>42.472296</v>
       </c>
       <c r="N80">
-        <v>-25.644672</v>
+        <v>-26.182296</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-25.644672</v>
+        <v>-26.182296</v>
       </c>
       <c r="Q80">
-        <v>-10.434672</v>
+        <v>-10.972296</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1896761737666628</v>
+        <v>0.1965274201365039</v>
       </c>
       <c r="T80">
-        <v>2.804414423293664</v>
+        <v>2.937957967260029</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3884613667659067</v>
+        <v>0.3835441342751991</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2275527582286658</v>
+        <v>0.2294527582286658</v>
       </c>
       <c r="C81">
-        <v>-87.85294687982122</v>
+        <v>-90.51642819318462</v>
       </c>
       <c r="D81">
-        <v>37.06705312017879</v>
+        <v>36.68357180681537</v>
       </c>
       <c r="E81">
-        <v>40.02000000000001</v>
+        <v>42.30000000000001</v>
       </c>
       <c r="F81">
-        <v>180.12</v>
+        <v>182.4</v>
       </c>
       <c r="G81">
         <v>55.2</v>
@@ -7923,28 +7923,28 @@
         <v>16.29</v>
       </c>
       <c r="M81">
-        <v>42.472296</v>
+        <v>43.00992</v>
       </c>
       <c r="N81">
-        <v>-26.182296</v>
+        <v>-26.71992</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-26.182296</v>
+        <v>-26.71992</v>
       </c>
       <c r="Q81">
-        <v>-10.972296</v>
+        <v>-11.50992</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1965274201365039</v>
+        <v>0.2040637911433291</v>
       </c>
       <c r="T81">
-        <v>2.937957967260029</v>
+        <v>3.08485586562303</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3835441342751991</v>
+        <v>0.3787498325967591</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2294527582286658</v>
+        <v>0.2313527582286658</v>
       </c>
       <c r="C82">
-        <v>-90.51642819318462</v>
+        <v>-93.17205605826361</v>
       </c>
       <c r="D82">
-        <v>36.68357180681537</v>
+        <v>36.3079439417364</v>
       </c>
       <c r="E82">
-        <v>42.30000000000001</v>
+        <v>44.58000000000001</v>
       </c>
       <c r="F82">
-        <v>182.4</v>
+        <v>184.68</v>
       </c>
       <c r="G82">
         <v>55.2</v>
@@ -8005,28 +8005,28 @@
         <v>16.29</v>
       </c>
       <c r="M82">
-        <v>43.00992</v>
+        <v>43.547544</v>
       </c>
       <c r="N82">
-        <v>-26.71992</v>
+        <v>-27.257544</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-26.71992</v>
+        <v>-27.257544</v>
       </c>
       <c r="Q82">
-        <v>-11.50992</v>
+        <v>-12.047544</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2040637911433291</v>
+        <v>0.2123934643613991</v>
       </c>
       <c r="T82">
-        <v>3.08485586562303</v>
+        <v>3.247216700655821</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3787498325967591</v>
+        <v>0.3740739087375398</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2313527582286658</v>
+        <v>0.2332527582286658</v>
       </c>
       <c r="C83">
-        <v>-93.17205605826361</v>
+        <v>-95.82006928005438</v>
       </c>
       <c r="D83">
-        <v>36.3079439417364</v>
+        <v>35.93993071994561</v>
       </c>
       <c r="E83">
-        <v>44.58000000000001</v>
+        <v>46.86000000000001</v>
       </c>
       <c r="F83">
-        <v>184.68</v>
+        <v>186.96</v>
       </c>
       <c r="G83">
         <v>55.2</v>
@@ -8087,28 +8087,28 @@
         <v>16.29</v>
       </c>
       <c r="M83">
-        <v>43.547544</v>
+        <v>44.085168</v>
       </c>
       <c r="N83">
-        <v>-27.257544</v>
+        <v>-27.795168</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-27.257544</v>
+        <v>-27.795168</v>
       </c>
       <c r="Q83">
-        <v>-12.047544</v>
+        <v>-12.585168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2123934643613991</v>
+        <v>0.2216486568259212</v>
       </c>
       <c r="T83">
-        <v>3.247216700655821</v>
+        <v>3.427617628470034</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3740739087375398</v>
+        <v>0.3695120318017161</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2332527582286658</v>
+        <v>0.2351527582286658</v>
       </c>
       <c r="C84">
-        <v>-95.82006928005438</v>
+        <v>-98.4606970787022</v>
       </c>
       <c r="D84">
-        <v>35.93993071994561</v>
+        <v>35.57930292129782</v>
       </c>
       <c r="E84">
-        <v>46.86000000000001</v>
+        <v>49.14000000000001</v>
       </c>
       <c r="F84">
-        <v>186.96</v>
+        <v>189.24</v>
       </c>
       <c r="G84">
         <v>55.2</v>
@@ -8169,28 +8169,28 @@
         <v>16.29</v>
       </c>
       <c r="M84">
-        <v>44.085168</v>
+        <v>44.622792</v>
       </c>
       <c r="N84">
-        <v>-27.795168</v>
+        <v>-28.332792</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-27.795168</v>
+        <v>-28.332792</v>
       </c>
       <c r="Q84">
-        <v>-12.585168</v>
+        <v>-13.12279200000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2216486568259212</v>
+        <v>0.2319926954627402</v>
       </c>
       <c r="T84">
-        <v>3.427617628470034</v>
+        <v>3.629242194850625</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3695120318017161</v>
+        <v>0.365060079611334</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2351527582286658</v>
+        <v>0.2370527582286658</v>
       </c>
       <c r="C85">
-        <v>-98.4606970787022</v>
+        <v>-101.0941595656047</v>
       </c>
       <c r="D85">
-        <v>35.57930292129782</v>
+        <v>35.22584043439532</v>
       </c>
       <c r="E85">
-        <v>49.14000000000001</v>
+        <v>51.42000000000002</v>
       </c>
       <c r="F85">
-        <v>189.24</v>
+        <v>191.52</v>
       </c>
       <c r="G85">
         <v>55.2</v>
@@ -8251,28 +8251,28 @@
         <v>16.29</v>
       </c>
       <c r="M85">
-        <v>44.622792</v>
+        <v>45.160416</v>
       </c>
       <c r="N85">
-        <v>-28.332792</v>
+        <v>-28.87041600000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-28.332792</v>
+        <v>-28.87041600000001</v>
       </c>
       <c r="Q85">
-        <v>-13.12279200000001</v>
+        <v>-13.66041600000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2319926954627402</v>
+        <v>0.2436297389291615</v>
       </c>
       <c r="T85">
-        <v>3.629242194850625</v>
+        <v>3.856069832028789</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.365060079611334</v>
+        <v>0.3607141262826277</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2370527582286658</v>
+        <v>0.2389527582286658</v>
       </c>
       <c r="C86">
-        <v>-101.0941595656047</v>
+        <v>-103.7206681914153</v>
       </c>
       <c r="D86">
-        <v>35.22584043439532</v>
+        <v>34.87933180858466</v>
       </c>
       <c r="E86">
-        <v>51.41999999999999</v>
+        <v>53.69999999999999</v>
       </c>
       <c r="F86">
-        <v>191.52</v>
+        <v>193.8</v>
       </c>
       <c r="G86">
         <v>55.2</v>
@@ -8333,28 +8333,28 @@
         <v>16.29</v>
       </c>
       <c r="M86">
-        <v>45.160416</v>
+        <v>45.69804</v>
       </c>
       <c r="N86">
-        <v>-28.870416</v>
+        <v>-29.40804</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-28.870416</v>
+        <v>-29.40804</v>
       </c>
       <c r="Q86">
-        <v>-13.660416</v>
+        <v>-14.19804</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2436297389291613</v>
+        <v>0.2568183881911054</v>
       </c>
       <c r="T86">
-        <v>3.856069832028787</v>
+        <v>4.113141154164039</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3607141262826277</v>
+        <v>0.3564704306793026</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2389527582286658</v>
+        <v>0.2408527582286658</v>
       </c>
       <c r="C87">
-        <v>-103.7206681914153</v>
+        <v>-106.340426167863</v>
       </c>
       <c r="D87">
-        <v>34.87933180858466</v>
+        <v>34.53957383213697</v>
       </c>
       <c r="E87">
-        <v>53.69999999999999</v>
+        <v>55.97999999999999</v>
       </c>
       <c r="F87">
-        <v>193.8</v>
+        <v>196.08</v>
       </c>
       <c r="G87">
         <v>55.2</v>
@@ -8415,28 +8415,28 @@
         <v>16.29</v>
       </c>
       <c r="M87">
-        <v>45.69804</v>
+        <v>46.235664</v>
       </c>
       <c r="N87">
-        <v>-29.40804</v>
+        <v>-29.945664</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-29.40804</v>
+        <v>-29.945664</v>
       </c>
       <c r="Q87">
-        <v>-14.19804</v>
+        <v>-14.735664</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2568183881911054</v>
+        <v>0.2718911302047558</v>
       </c>
       <c r="T87">
-        <v>4.113141154164039</v>
+        <v>4.406936950890042</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3564704306793026</v>
+        <v>0.3523254256714038</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2408527582286658</v>
+        <v>0.2427527582286658</v>
       </c>
       <c r="C88">
-        <v>-106.340426167863</v>
+        <v>-108.9536288651558</v>
       </c>
       <c r="D88">
-        <v>34.53957383213697</v>
+        <v>34.20637113484413</v>
       </c>
       <c r="E88">
-        <v>55.97999999999999</v>
+        <v>58.25999999999999</v>
       </c>
       <c r="F88">
-        <v>196.08</v>
+        <v>198.36</v>
       </c>
       <c r="G88">
         <v>55.2</v>
@@ -8497,28 +8497,28 @@
         <v>16.29</v>
       </c>
       <c r="M88">
-        <v>46.235664</v>
+        <v>46.773288</v>
       </c>
       <c r="N88">
-        <v>-29.945664</v>
+        <v>-30.483288</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-29.945664</v>
+        <v>-30.483288</v>
       </c>
       <c r="Q88">
-        <v>-14.735664</v>
+        <v>-15.273288</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2718911302047558</v>
+        <v>0.2892827556051216</v>
       </c>
       <c r="T88">
-        <v>4.406936950890042</v>
+        <v>4.745932100958506</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3523254256714038</v>
+        <v>0.3482757081349509</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2427527582286658</v>
+        <v>0.2446527582286658</v>
       </c>
       <c r="C89">
-        <v>-108.9536288651558</v>
+        <v>-111.5604641866025</v>
       </c>
       <c r="D89">
-        <v>34.20637113484413</v>
+        <v>33.87953581339754</v>
       </c>
       <c r="E89">
-        <v>58.25999999999999</v>
+        <v>60.54000000000002</v>
       </c>
       <c r="F89">
-        <v>198.36</v>
+        <v>200.64</v>
       </c>
       <c r="G89">
         <v>55.2</v>
@@ -8579,28 +8579,28 @@
         <v>16.29</v>
       </c>
       <c r="M89">
-        <v>46.773288</v>
+        <v>47.31091200000001</v>
       </c>
       <c r="N89">
-        <v>-30.483288</v>
+        <v>-31.02091200000001</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-30.483288</v>
+        <v>-31.02091200000001</v>
       </c>
       <c r="Q89">
-        <v>-15.273288</v>
+        <v>-15.81091200000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2892827556051216</v>
+        <v>0.3095729852388818</v>
       </c>
       <c r="T89">
-        <v>4.745932100958506</v>
+        <v>5.14142644270505</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3482757081349509</v>
+        <v>0.3443180296334173</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2446527582286658</v>
+        <v>0.2465527582286658</v>
       </c>
       <c r="C90">
-        <v>-111.5604641866025</v>
+        <v>-114.1611129219595</v>
       </c>
       <c r="D90">
-        <v>33.87953581339754</v>
+        <v>33.55888707804053</v>
       </c>
       <c r="E90">
-        <v>60.54000000000002</v>
+        <v>62.82000000000002</v>
       </c>
       <c r="F90">
-        <v>200.64</v>
+        <v>202.92</v>
       </c>
       <c r="G90">
         <v>55.2</v>
@@ -8661,28 +8661,28 @@
         <v>16.29</v>
       </c>
       <c r="M90">
-        <v>47.31091200000001</v>
+        <v>47.848536</v>
       </c>
       <c r="N90">
-        <v>-31.02091200000001</v>
+        <v>-31.558536</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-31.02091200000001</v>
+        <v>-31.558536</v>
       </c>
       <c r="Q90">
-        <v>-15.81091200000001</v>
+        <v>-16.348536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3095729852388818</v>
+        <v>0.3335523475333256</v>
       </c>
       <c r="T90">
-        <v>5.14142644270505</v>
+        <v>5.608828846587327</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3443180296334173</v>
+        <v>0.3404492877274239</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2465527582286658</v>
+        <v>0.2484527582286658</v>
       </c>
       <c r="C91">
-        <v>-114.1611129219595</v>
+        <v>-116.7557490809025</v>
       </c>
       <c r="D91">
-        <v>33.55888707804053</v>
+        <v>33.2442509190975</v>
       </c>
       <c r="E91">
-        <v>62.82000000000002</v>
+        <v>65.10000000000002</v>
       </c>
       <c r="F91">
-        <v>202.92</v>
+        <v>205.2</v>
       </c>
       <c r="G91">
         <v>55.2</v>
@@ -8743,28 +8743,28 @@
         <v>16.29</v>
       </c>
       <c r="M91">
-        <v>47.848536</v>
+        <v>48.38616</v>
       </c>
       <c r="N91">
-        <v>-31.558536</v>
+        <v>-32.09616</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-31.558536</v>
+        <v>-32.09616</v>
       </c>
       <c r="Q91">
-        <v>-16.348536</v>
+        <v>-16.88616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3335523475333256</v>
+        <v>0.3623275822866582</v>
       </c>
       <c r="T91">
-        <v>5.608828846587327</v>
+        <v>6.169711731246061</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3404492877274239</v>
+        <v>0.3366665178637858</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2484527582286658</v>
+        <v>0.2503527582286658</v>
       </c>
       <c r="C92">
-        <v>-116.7557490809025</v>
+        <v>-119.3445402079118</v>
       </c>
       <c r="D92">
-        <v>33.2442509190975</v>
+        <v>32.93545979208824</v>
       </c>
       <c r="E92">
-        <v>65.10000000000002</v>
+        <v>67.38000000000002</v>
       </c>
       <c r="F92">
-        <v>205.2</v>
+        <v>207.48</v>
       </c>
       <c r="G92">
         <v>55.2</v>
@@ -8825,28 +8825,28 @@
         <v>16.29</v>
       </c>
       <c r="M92">
-        <v>48.38616</v>
+        <v>48.923784</v>
       </c>
       <c r="N92">
-        <v>-32.09616</v>
+        <v>-32.63378400000001</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-32.09616</v>
+        <v>-32.63378400000001</v>
       </c>
       <c r="Q92">
-        <v>-16.88616</v>
+        <v>-17.423784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3623275822866582</v>
+        <v>0.3974973136518425</v>
       </c>
       <c r="T92">
-        <v>6.169711731246061</v>
+        <v>6.855235256940068</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3366665178637858</v>
+        <v>0.3329668857993486</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2503527582286658</v>
+        <v>0.2522527582286658</v>
       </c>
       <c r="C93">
-        <v>-119.3445402079118</v>
+        <v>-121.9276476797706</v>
       </c>
       <c r="D93">
-        <v>32.93545979208824</v>
+        <v>32.63235232022943</v>
       </c>
       <c r="E93">
-        <v>67.38000000000002</v>
+        <v>69.66000000000003</v>
       </c>
       <c r="F93">
-        <v>207.48</v>
+        <v>209.76</v>
       </c>
       <c r="G93">
         <v>55.2</v>
@@ -8907,28 +8907,28 @@
         <v>16.29</v>
       </c>
       <c r="M93">
-        <v>48.923784</v>
+        <v>49.46140800000001</v>
       </c>
       <c r="N93">
-        <v>-32.63378400000001</v>
+        <v>-33.17140800000001</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-32.63378400000001</v>
+        <v>-33.17140800000001</v>
       </c>
       <c r="Q93">
-        <v>-17.423784</v>
+        <v>-17.96140800000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3974973136518425</v>
+        <v>0.4414594778583229</v>
       </c>
       <c r="T93">
-        <v>6.855235256940068</v>
+        <v>7.712139664057578</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3329668857993486</v>
+        <v>0.3293476805189208</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2522527582286658</v>
+        <v>0.2541527582286658</v>
       </c>
       <c r="C94">
-        <v>-121.9276476797706</v>
+        <v>-124.505226986786</v>
       </c>
       <c r="D94">
-        <v>32.63235232022943</v>
+        <v>32.33477301321401</v>
       </c>
       <c r="E94">
-        <v>69.66000000000003</v>
+        <v>71.94000000000003</v>
       </c>
       <c r="F94">
-        <v>209.76</v>
+        <v>212.04</v>
       </c>
       <c r="G94">
         <v>55.2</v>
@@ -8989,28 +8989,28 @@
         <v>16.29</v>
       </c>
       <c r="M94">
-        <v>49.46140800000001</v>
+        <v>49.99903200000001</v>
       </c>
       <c r="N94">
-        <v>-33.17140800000001</v>
+        <v>-33.70903200000001</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-33.17140800000001</v>
+        <v>-33.70903200000001</v>
       </c>
       <c r="Q94">
-        <v>-17.96140800000001</v>
+        <v>-18.49903200000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4414594778583229</v>
+        <v>0.4979822604095119</v>
       </c>
       <c r="T94">
-        <v>7.712139664057578</v>
+        <v>8.81387390178009</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3293476805189208</v>
+        <v>0.3258063076101153</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2541527582286658</v>
+        <v>0.2560527582286658</v>
       </c>
       <c r="C95">
-        <v>-124.505226986786</v>
+        <v>-127.0774279987617</v>
       </c>
       <c r="D95">
-        <v>32.33477301321401</v>
+        <v>32.04257200123827</v>
       </c>
       <c r="E95">
-        <v>71.94000000000003</v>
+        <v>74.22000000000003</v>
       </c>
       <c r="F95">
-        <v>212.04</v>
+        <v>214.32</v>
       </c>
       <c r="G95">
         <v>55.2</v>
@@ -9071,28 +9071,28 @@
         <v>16.29</v>
       </c>
       <c r="M95">
-        <v>49.99903200000001</v>
+        <v>50.53665600000001</v>
       </c>
       <c r="N95">
-        <v>-33.70903200000001</v>
+        <v>-34.24665600000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-33.70903200000001</v>
+        <v>-34.24665600000001</v>
       </c>
       <c r="Q95">
-        <v>-18.49903200000001</v>
+        <v>-19.03665600000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4979822604095119</v>
+        <v>0.5733459704777639</v>
       </c>
       <c r="T95">
-        <v>8.81387390178009</v>
+        <v>10.28285288541011</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3258063076101153</v>
+        <v>0.3223402830610714</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2560527582286658</v>
+        <v>0.2579527582286658</v>
       </c>
       <c r="C96">
-        <v>-127.0774279987617</v>
+        <v>-129.644395216679</v>
       </c>
       <c r="D96">
-        <v>32.04257200123827</v>
+        <v>31.75560478332101</v>
       </c>
       <c r="E96">
-        <v>74.22000000000003</v>
+        <v>76.50000000000003</v>
       </c>
       <c r="F96">
-        <v>214.32</v>
+        <v>216.6</v>
       </c>
       <c r="G96">
         <v>55.2</v>
@@ -9153,28 +9153,28 @@
         <v>16.29</v>
       </c>
       <c r="M96">
-        <v>50.53665600000001</v>
+        <v>51.07428000000001</v>
       </c>
       <c r="N96">
-        <v>-34.24665600000001</v>
+        <v>-34.78428000000001</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-34.24665600000001</v>
+        <v>-34.78428000000001</v>
       </c>
       <c r="Q96">
-        <v>-19.03665600000001</v>
+        <v>-19.57428000000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5733459704777639</v>
+        <v>0.6788551645733171</v>
       </c>
       <c r="T96">
-        <v>10.28285288541011</v>
+        <v>12.33942346249214</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3223402830610714</v>
+        <v>0.3189472274499023</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2579527582286658</v>
+        <v>0.2598527582286658</v>
       </c>
       <c r="C97">
-        <v>-129.644395216679</v>
+        <v>-132.2062680109733</v>
       </c>
       <c r="D97">
-        <v>31.75560478332101</v>
+        <v>31.47373198902674</v>
       </c>
       <c r="E97">
-        <v>76.50000000000003</v>
+        <v>78.78000000000003</v>
       </c>
       <c r="F97">
-        <v>216.6</v>
+        <v>218.88</v>
       </c>
       <c r="G97">
         <v>55.2</v>
@@ -9235,28 +9235,28 @@
         <v>16.29</v>
       </c>
       <c r="M97">
-        <v>51.07428000000001</v>
+        <v>51.61190400000001</v>
       </c>
       <c r="N97">
-        <v>-34.78428000000001</v>
+        <v>-35.32190400000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-34.78428000000001</v>
+        <v>-35.32190400000001</v>
       </c>
       <c r="Q97">
-        <v>-19.57428000000001</v>
+        <v>-20.11190400000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6788551645733171</v>
+        <v>0.8371189557166467</v>
       </c>
       <c r="T97">
-        <v>12.33942346249214</v>
+        <v>15.42427932811518</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3189472274499023</v>
+        <v>0.3156248604972991</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2598527582286658</v>
+        <v>0.2617527582286658</v>
       </c>
       <c r="C98">
-        <v>-132.2062680109732</v>
+        <v>-134.7631808472327</v>
       </c>
       <c r="D98">
-        <v>31.47373198902674</v>
+        <v>31.19681915276729</v>
       </c>
       <c r="E98">
-        <v>78.78</v>
+        <v>81.06</v>
       </c>
       <c r="F98">
-        <v>218.88</v>
+        <v>221.16</v>
       </c>
       <c r="G98">
         <v>55.2</v>
@@ -9317,28 +9317,28 @@
         <v>16.29</v>
       </c>
       <c r="M98">
-        <v>51.611904</v>
+        <v>52.149528</v>
       </c>
       <c r="N98">
-        <v>-35.321904</v>
+        <v>-35.859528</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-35.321904</v>
+        <v>-35.859528</v>
       </c>
       <c r="Q98">
-        <v>-20.111904</v>
+        <v>-20.649528</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8371189557166446</v>
+        <v>1.100891940955526</v>
       </c>
       <c r="T98">
-        <v>15.42427932811514</v>
+        <v>20.56570577082018</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3156248604972992</v>
+        <v>0.31237099595609</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2617527582286658</v>
+        <v>0.2636527582286659</v>
       </c>
       <c r="C99">
-        <v>-134.7631808472327</v>
+        <v>-137.315263500086</v>
       </c>
       <c r="D99">
-        <v>31.19681915276729</v>
+        <v>30.92473649991402</v>
       </c>
       <c r="E99">
-        <v>81.06</v>
+        <v>83.34</v>
       </c>
       <c r="F99">
-        <v>221.16</v>
+        <v>223.44</v>
       </c>
       <c r="G99">
         <v>55.2</v>
@@ -9399,28 +9399,28 @@
         <v>16.29</v>
       </c>
       <c r="M99">
-        <v>52.149528</v>
+        <v>52.687152</v>
       </c>
       <c r="N99">
-        <v>-35.859528</v>
+        <v>-36.39715200000001</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-35.859528</v>
+        <v>-36.39715200000001</v>
       </c>
       <c r="Q99">
-        <v>-20.649528</v>
+        <v>-21.187152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.100891940955526</v>
+        <v>1.628437911433289</v>
       </c>
       <c r="T99">
-        <v>20.56570577082018</v>
+        <v>30.84855865623027</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.31237099595609</v>
+        <v>0.3091835368136808</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2636527582286659</v>
+        <v>0.2655527582286658</v>
       </c>
       <c r="C100">
-        <v>-137.315263500086</v>
+        <v>-139.8626412559942</v>
       </c>
       <c r="D100">
-        <v>30.92473649991402</v>
+        <v>30.65735874400575</v>
       </c>
       <c r="E100">
-        <v>83.34</v>
+        <v>85.62</v>
       </c>
       <c r="F100">
-        <v>223.44</v>
+        <v>225.72</v>
       </c>
       <c r="G100">
         <v>55.2</v>
@@ -9481,28 +9481,28 @@
         <v>16.29</v>
       </c>
       <c r="M100">
-        <v>52.687152</v>
+        <v>53.224776</v>
       </c>
       <c r="N100">
-        <v>-36.39715200000001</v>
+        <v>-36.934776</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-36.39715200000001</v>
+        <v>-36.934776</v>
       </c>
       <c r="Q100">
-        <v>-21.187152</v>
+        <v>-21.724776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.628437911433289</v>
+        <v>3.211075822866579</v>
       </c>
       <c r="T100">
-        <v>30.84855865623027</v>
+        <v>61.69711731246054</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3091835368136808</v>
+        <v>0.3060604707852599</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2655527582286658</v>
-      </c>
-      <c r="C101">
-        <v>-139.8626412559942</v>
-      </c>
-      <c r="D101">
-        <v>30.65735874400575</v>
-      </c>
-      <c r="E101">
-        <v>85.62</v>
-      </c>
-      <c r="F101">
-        <v>225.72</v>
-      </c>
-      <c r="G101">
-        <v>55.2</v>
-      </c>
-      <c r="H101">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.5</v>
-      </c>
-      <c r="K101">
-        <v>15.21</v>
-      </c>
-      <c r="L101">
-        <v>16.29</v>
-      </c>
-      <c r="M101">
-        <v>53.224776</v>
-      </c>
-      <c r="N101">
-        <v>-36.934776</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-36.934776</v>
-      </c>
-      <c r="Q101">
-        <v>-21.724776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.211075822866579</v>
-      </c>
-      <c r="T101">
-        <v>61.69711731246054</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3060604707852599</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
